--- a/MIO_Spielplan.xlsx
+++ b/MIO_Spielplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44A56A9-6B0E-1D40-899D-77A9259EDA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D608115-CF13-9149-BBCF-22F4E272B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="17" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="36">
   <si>
     <t>Klasse</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>2b</t>
-  </si>
-  <si>
-    <t>67|68</t>
-  </si>
-  <si>
-    <t>69|70</t>
   </si>
   <si>
     <t>73|74</t>
@@ -78,37 +72,10 @@
     <t>2e</t>
   </si>
   <si>
-    <t>18|19</t>
-  </si>
-  <si>
     <t>2a</t>
   </si>
   <si>
-    <t>50|51</t>
-  </si>
-  <si>
-    <t>58|59</t>
-  </si>
-  <si>
     <t>2d</t>
-  </si>
-  <si>
-    <t>26|27</t>
-  </si>
-  <si>
-    <t>28|29</t>
-  </si>
-  <si>
-    <t>30|31</t>
-  </si>
-  <si>
-    <t>32|33</t>
-  </si>
-  <si>
-    <t>34|35</t>
-  </si>
-  <si>
-    <t>36|37</t>
   </si>
   <si>
     <t>Zeit</t>
@@ -142,78 +109,6 @@
   </si>
   <si>
     <t>Runde 6</t>
-  </si>
-  <si>
-    <t>52|53</t>
-  </si>
-  <si>
-    <t>54|55</t>
-  </si>
-  <si>
-    <t>1|2</t>
-  </si>
-  <si>
-    <t>3|4</t>
-  </si>
-  <si>
-    <t>5|6</t>
-  </si>
-  <si>
-    <t>7|8</t>
-  </si>
-  <si>
-    <t>9|10</t>
-  </si>
-  <si>
-    <t>11|12</t>
-  </si>
-  <si>
-    <t>14|20</t>
-  </si>
-  <si>
-    <t>15|16</t>
-  </si>
-  <si>
-    <t>17|21</t>
-  </si>
-  <si>
-    <t>22|24</t>
-  </si>
-  <si>
-    <t>23|25</t>
-  </si>
-  <si>
-    <t>56|57</t>
-  </si>
-  <si>
-    <t>61|62</t>
-  </si>
-  <si>
-    <t>63|64</t>
-  </si>
-  <si>
-    <t>65|66</t>
-  </si>
-  <si>
-    <t>83|89</t>
-  </si>
-  <si>
-    <t>84|85</t>
-  </si>
-  <si>
-    <t>86|87</t>
-  </si>
-  <si>
-    <t>88|92</t>
-  </si>
-  <si>
-    <t>90|93</t>
-  </si>
-  <si>
-    <t>91|94</t>
-  </si>
-  <si>
-    <t>71|72</t>
   </si>
   <si>
     <t>13:30-13:40</t>
@@ -823,14 +718,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2260,24 +2155,24 @@
       <c r="L1" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
+      <c r="A3" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A4" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4" s="47"/>
       <c r="C4" s="47"/>
@@ -2286,7 +2181,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
       <c r="H4" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
@@ -2295,16 +2190,16 @@
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>0</v>
@@ -2312,16 +2207,16 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>0</v>
@@ -2330,16 +2225,16 @@
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A6" s="55" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>11</v>
+      </c>
+      <c r="C6" s="16">
+        <v>57</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>2</v>
@@ -2347,16 +2242,16 @@
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
       <c r="H6" s="55" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>50</v>
+        <v>9</v>
+      </c>
+      <c r="J6" s="16">
+        <v>10</v>
+      </c>
+      <c r="K6" s="21">
+        <v>63</v>
       </c>
       <c r="L6" s="22" t="s">
         <v>1</v>
@@ -2365,58 +2260,58 @@
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A7" s="55"/>
       <c r="B7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="16">
+        <v>6</v>
+      </c>
+      <c r="D7" s="21">
+        <v>32</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
       <c r="H7" s="55"/>
       <c r="I7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>53</v>
+        <v>10</v>
+      </c>
+      <c r="J7" s="16">
+        <v>15</v>
+      </c>
+      <c r="K7" s="21">
+        <v>84</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A8" s="55"/>
       <c r="B8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>56</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="16">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21">
+        <v>93</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
       <c r="H8" s="55"/>
       <c r="I8" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="J8" s="16">
+        <v>51</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" s="22" t="s">
         <v>2</v>
@@ -2425,13 +2320,13 @@
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A9" s="55"/>
       <c r="B9" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C9" s="16">
+        <v>59</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>2</v>
@@ -2440,28 +2335,28 @@
       <c r="G9" s="5"/>
       <c r="H9" s="55"/>
       <c r="I9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="16">
         <v>11</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>22</v>
+      <c r="K9" s="21">
+        <v>35</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="22" thickBot="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="56"/>
       <c r="B10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>49</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="18">
+        <v>8</v>
+      </c>
+      <c r="D10" s="23">
+        <v>62</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>1</v>
@@ -2470,13 +2365,13 @@
       <c r="G10" s="5"/>
       <c r="H10" s="56"/>
       <c r="I10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>58</v>
+        <v>10</v>
+      </c>
+      <c r="J10" s="29">
+        <v>23</v>
+      </c>
+      <c r="K10" s="23">
+        <v>71</v>
       </c>
       <c r="L10" s="24" t="s">
         <v>1</v>
@@ -2484,48 +2379,48 @@
     </row>
     <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A11" s="53" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="C11" s="20">
+        <v>22</v>
+      </c>
+      <c r="D11" s="25">
+        <v>92</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
       <c r="H11" s="53" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+      <c r="K11" s="25">
+        <v>29</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A12" s="54"/>
       <c r="B12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="C12" s="16">
+        <v>53</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>2</v>
@@ -2534,58 +2429,58 @@
       <c r="G12" s="5"/>
       <c r="H12" s="54"/>
       <c r="I12" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>54</v>
+        <v>10</v>
+      </c>
+      <c r="J12" s="16">
+        <v>17</v>
+      </c>
+      <c r="K12" s="21">
+        <v>86</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A13" s="54"/>
       <c r="B13" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="C13" s="16">
+        <v>3</v>
+      </c>
+      <c r="D13" s="21">
+        <v>31</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
       <c r="H13" s="54"/>
       <c r="I13" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="16">
+        <v>26</v>
+      </c>
+      <c r="K13" s="21">
+        <v>83</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A14" s="54"/>
       <c r="B14" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="16">
+        <v>20</v>
+      </c>
+      <c r="D14" s="21">
+        <v>69</v>
       </c>
       <c r="E14" s="22" t="s">
         <v>1</v>
@@ -2594,13 +2489,13 @@
       <c r="G14" s="5"/>
       <c r="H14" s="54"/>
       <c r="I14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="J14" s="16">
+        <v>94</v>
+      </c>
+      <c r="K14" s="21">
+        <v>66</v>
       </c>
       <c r="L14" s="22" t="s">
         <v>1</v>
@@ -2609,13 +2504,13 @@
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
       <c r="A15" s="54"/>
       <c r="B15" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="C15" s="16">
+        <v>55</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>2</v>
@@ -2626,14 +2521,14 @@
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>23</v>
+      <c r="J15" s="16">
+        <v>68</v>
+      </c>
+      <c r="K15" s="21">
+        <v>36</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.15">
@@ -2665,24 +2560,24 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="50"/>
+      <c r="A18" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A19" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
@@ -2691,7 +2586,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="3"/>
       <c r="H19" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I19" s="47"/>
       <c r="J19" s="47"/>
@@ -2700,16 +2595,16 @@
     </row>
     <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>0</v>
@@ -2717,53 +2612,53 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A21" s="55" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>40</v>
+        <v>11</v>
+      </c>
+      <c r="C21" s="27">
+        <v>59</v>
+      </c>
+      <c r="D21" s="21">
+        <v>8</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
       <c r="H21" s="55" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="J21" s="16">
+        <v>83</v>
+      </c>
+      <c r="K21" s="39">
+        <v>23</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -2772,40 +2667,40 @@
         <v>2</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="D22" s="21">
+        <v>29</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5"/>
       <c r="H22" s="55"/>
       <c r="I22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="J22" s="16">
+        <v>55</v>
+      </c>
+      <c r="K22" s="21">
+        <v>6</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A23" s="55"/>
       <c r="B23" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="C23" s="28">
+        <v>22</v>
+      </c>
+      <c r="D23" s="21">
+        <v>68</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>1</v>
@@ -2817,40 +2712,40 @@
         <v>2</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="21" t="s">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="K23" s="21">
+        <v>26</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A24" s="55"/>
       <c r="B24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="C24" s="16">
+        <v>93</v>
+      </c>
+      <c r="D24" s="21">
+        <v>3</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
       <c r="H24" s="55"/>
       <c r="I24" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="J24" s="16">
+        <v>17</v>
+      </c>
+      <c r="K24" s="21">
+        <v>62</v>
       </c>
       <c r="L24" s="22" t="s">
         <v>1</v>
@@ -2859,28 +2754,28 @@
     <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="56"/>
       <c r="B25" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="C25" s="29">
+        <v>57</v>
+      </c>
+      <c r="D25" s="23">
+        <v>1</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
       <c r="H25" s="56"/>
       <c r="I25" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="J25" s="29">
+        <v>84</v>
+      </c>
+      <c r="K25" s="23">
+        <v>69</v>
       </c>
       <c r="L25" s="24" t="s">
         <v>1</v>
@@ -2888,48 +2783,48 @@
     </row>
     <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A26" s="53" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="D26" s="25">
+        <v>32</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
       <c r="H26" s="53" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="J26" s="20">
+        <v>51</v>
+      </c>
+      <c r="K26" s="25">
+        <v>11</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A27" s="54"/>
       <c r="B27" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="C27" s="16">
+        <v>18</v>
+      </c>
+      <c r="D27" s="21">
+        <v>63</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>1</v>
@@ -2941,40 +2836,40 @@
         <v>2</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="21" t="s">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="K27" s="21">
+        <v>31</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A28" s="54"/>
       <c r="B28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="C28" s="16">
+        <v>86</v>
+      </c>
+      <c r="D28" s="21">
+        <v>36</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
       <c r="H28" s="54"/>
       <c r="I28" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="K28" s="21" t="s">
-        <v>51</v>
+        <v>10</v>
+      </c>
+      <c r="J28" s="16">
+        <v>15</v>
+      </c>
+      <c r="K28" s="21">
+        <v>66</v>
       </c>
       <c r="L28" s="22" t="s">
         <v>1</v>
@@ -2983,31 +2878,31 @@
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A29" s="54"/>
       <c r="B29" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="C29" s="16">
+        <v>53</v>
+      </c>
+      <c r="D29" s="21">
+        <v>10</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
       <c r="H29" s="54"/>
       <c r="I29" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" s="21" t="s">
-        <v>57</v>
+        <v>10</v>
+      </c>
+      <c r="J29" s="16">
+        <v>20</v>
+      </c>
+      <c r="K29" s="21">
+        <v>94</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3016,13 +2911,13 @@
         <v>2</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="D30" s="21">
+        <v>35</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
@@ -3030,14 +2925,14 @@
       <c r="I30" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J30" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="K30" s="21" t="s">
-        <v>55</v>
+      <c r="J30" s="16">
+        <v>71</v>
+      </c>
+      <c r="K30" s="21">
+        <v>92</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.15">
@@ -3069,24 +2964,24 @@
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
+      <c r="A33" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
     </row>
     <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A34" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B34" s="47"/>
       <c r="C34" s="47"/>
@@ -3095,7 +2990,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
       <c r="H34" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I34" s="47"/>
       <c r="J34" s="47"/>
@@ -3104,16 +2999,16 @@
     </row>
     <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>0</v>
@@ -3121,16 +3016,16 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>0</v>
@@ -3138,36 +3033,36 @@
     </row>
     <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A36" s="55" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="C36" s="27">
+        <v>59</v>
+      </c>
+      <c r="D36" s="35">
+        <v>29</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
       <c r="H36" s="55" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J36" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="J36" s="16">
+        <v>8</v>
+      </c>
+      <c r="K36" s="21">
+        <v>92</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3176,13 +3071,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>47</v>
+        <v>5</v>
+      </c>
+      <c r="D37" s="21">
+        <v>23</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
@@ -3190,44 +3085,44 @@
       <c r="I37" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="J37" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>45</v>
+      <c r="J37" s="32">
+        <v>63</v>
+      </c>
+      <c r="K37" s="2">
+        <v>17</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A38" s="55"/>
       <c r="B38" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>9</v>
+      </c>
+      <c r="C38" s="31">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>84</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
       <c r="H38" s="55"/>
       <c r="I38" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" s="28">
+        <v>53</v>
+      </c>
+      <c r="K38" s="21">
         <v>35</v>
       </c>
-      <c r="K38" s="21" t="s">
-        <v>22</v>
-      </c>
       <c r="L38" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3235,14 +3130,14 @@
       <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>42</v>
+      <c r="C39" s="16">
+        <v>69</v>
+      </c>
+      <c r="D39" s="21">
+        <v>11</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
@@ -3251,107 +3146,107 @@
         <v>2</v>
       </c>
       <c r="J39" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>46</v>
+        <v>4</v>
+      </c>
+      <c r="K39" s="2">
+        <v>22</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="56"/>
       <c r="B40" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>23</v>
+        <v>11</v>
+      </c>
+      <c r="C40" s="29">
+        <v>51</v>
+      </c>
+      <c r="D40" s="23">
+        <v>36</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
       <c r="H40" s="56"/>
       <c r="I40" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="J40" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="K40" s="23" t="s">
-        <v>54</v>
+        <v>9</v>
+      </c>
+      <c r="J40" s="29">
+        <v>6</v>
+      </c>
+      <c r="K40" s="23">
+        <v>86</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A41" s="53" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>44</v>
+        <v>6</v>
+      </c>
+      <c r="D41" s="25">
+        <v>15</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
       <c r="H41" s="53" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="J41" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="25" t="s">
-        <v>56</v>
+      <c r="J41" s="20">
+        <v>68</v>
+      </c>
+      <c r="K41" s="25">
+        <v>93</v>
       </c>
       <c r="L41" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A42" s="54"/>
       <c r="B42" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>57</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="32">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2">
+        <v>94</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
       <c r="H42" s="54"/>
       <c r="I42" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="J42" s="32">
+        <v>57</v>
+      </c>
+      <c r="K42" s="2">
+        <v>31</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3359,14 +3254,14 @@
       <c r="B43" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>18</v>
+      <c r="C43" s="16">
+        <v>71</v>
+      </c>
+      <c r="D43" s="21">
+        <v>26</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
@@ -3375,40 +3270,40 @@
         <v>2</v>
       </c>
       <c r="J43" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="K43" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="K43" s="21">
+        <v>18</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A44" s="54"/>
       <c r="B44" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="C44" s="32">
+        <v>55</v>
+      </c>
+      <c r="D44" s="2">
+        <v>32</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
       <c r="H44" s="54"/>
       <c r="I44" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J44" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="21" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="J44" s="16">
+        <v>3</v>
+      </c>
+      <c r="K44" s="21">
+        <v>66</v>
       </c>
       <c r="L44" s="22" t="s">
         <v>1</v>
@@ -3420,25 +3315,25 @@
         <v>2</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>43</v>
+        <v>3</v>
+      </c>
+      <c r="D45" s="21">
+        <v>20</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
       <c r="H45" s="54"/>
       <c r="I45" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="K45" s="25" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="J45" s="20">
+        <v>83</v>
+      </c>
+      <c r="K45" s="25">
+        <v>62</v>
       </c>
       <c r="L45" s="26" t="s">
         <v>1</v>
@@ -3473,24 +3368,24 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="50"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="50"/>
+      <c r="A48" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="48"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
+      <c r="L48" s="48"/>
     </row>
     <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A49" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B49" s="47"/>
       <c r="C49" s="47"/>
@@ -3499,7 +3394,7 @@
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
       <c r="H49" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I49" s="47"/>
       <c r="J49" s="47"/>
@@ -3508,16 +3403,16 @@
     </row>
     <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>0</v>
@@ -3525,16 +3420,16 @@
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>0</v>
@@ -3542,36 +3437,36 @@
     </row>
     <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A51" s="55" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="C51" s="16">
+        <v>53</v>
+      </c>
+      <c r="D51" s="21">
+        <v>20</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
       <c r="H51" s="55" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J51" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K51" s="21" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="J51" s="16">
+        <v>3</v>
+      </c>
+      <c r="K51" s="21">
+        <v>36</v>
       </c>
       <c r="L51" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3580,40 +3475,40 @@
         <v>2</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>57</v>
+        <v>3</v>
+      </c>
+      <c r="D52" s="2">
+        <v>94</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
       <c r="H52" s="55"/>
       <c r="I52" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="J52" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="J52" s="32">
+        <v>84</v>
+      </c>
+      <c r="K52" s="2">
+        <v>63</v>
       </c>
       <c r="L52" s="34" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A53" s="55"/>
       <c r="B53" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="28">
         <v>11</v>
       </c>
-      <c r="C53" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>3</v>
+      <c r="D53" s="21">
+        <v>68</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>1</v>
@@ -3622,31 +3517,31 @@
       <c r="G53" s="5"/>
       <c r="H53" s="55"/>
       <c r="I53" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J53" s="28">
+        <v>51</v>
+      </c>
+      <c r="K53" s="21">
         <v>15</v>
       </c>
-      <c r="K53" s="21" t="s">
-        <v>44</v>
-      </c>
       <c r="L53" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A54" s="55"/>
       <c r="B54" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="C54" s="32">
+        <v>26</v>
+      </c>
+      <c r="D54" s="2">
+        <v>8</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
@@ -3655,40 +3550,40 @@
         <v>2</v>
       </c>
       <c r="J54" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>54</v>
+        <v>6</v>
+      </c>
+      <c r="K54" s="2">
+        <v>86</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A55" s="56"/>
       <c r="B55" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="C55" s="29">
+        <v>55</v>
+      </c>
+      <c r="D55" s="23">
+        <v>17</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
       <c r="H55" s="56"/>
       <c r="I55" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="J55" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="K55" s="23" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="J55" s="29">
+        <v>6</v>
+      </c>
+      <c r="K55" s="23">
+        <v>66</v>
       </c>
       <c r="L55" s="24" t="s">
         <v>1</v>
@@ -3696,33 +3591,33 @@
     </row>
     <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A56" s="53" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="D56" s="2">
+        <v>92</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
       <c r="H56" s="53" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="J56" s="32">
+        <v>31</v>
+      </c>
+      <c r="K56" s="2">
+        <v>62</v>
       </c>
       <c r="L56" s="34" t="s">
         <v>1</v>
@@ -3731,13 +3626,13 @@
     <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A57" s="54"/>
       <c r="B57" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C57" s="16">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21">
+        <v>71</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>1</v>
@@ -3746,31 +3641,31 @@
       <c r="G57" s="5"/>
       <c r="H57" s="54"/>
       <c r="I57" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="K57" s="21" t="s">
-        <v>47</v>
+        <v>11</v>
+      </c>
+      <c r="J57" s="16">
+        <v>57</v>
+      </c>
+      <c r="K57" s="21">
+        <v>23</v>
       </c>
       <c r="L57" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A58" s="54"/>
       <c r="B58" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
+      </c>
+      <c r="C58" s="32">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2">
+        <v>22</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
@@ -3779,43 +3674,43 @@
         <v>2</v>
       </c>
       <c r="J58" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>56</v>
+        <v>7</v>
+      </c>
+      <c r="K58" s="2">
+        <v>93</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A59" s="54"/>
       <c r="B59" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="C59" s="16">
+        <v>59</v>
+      </c>
+      <c r="D59" s="21">
+        <v>18</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
       <c r="H59" s="54"/>
       <c r="I59" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K59" s="21" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="J59" s="16">
+        <v>10</v>
+      </c>
+      <c r="K59" s="21">
+        <v>32</v>
       </c>
       <c r="L59" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3824,25 +3719,25 @@
         <v>2</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>52</v>
+        <v>4</v>
+      </c>
+      <c r="D60" s="25">
+        <v>83</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
       <c r="H60" s="54"/>
       <c r="I60" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="K60" s="25" t="s">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="J60" s="20">
+        <v>35</v>
+      </c>
+      <c r="K60" s="25">
+        <v>69</v>
       </c>
       <c r="L60" s="26" t="s">
         <v>1</v>
@@ -3877,24 +3772,24 @@
       <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B63" s="50"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="50"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
-      <c r="H63" s="50"/>
-      <c r="I63" s="50"/>
-      <c r="J63" s="50"/>
-      <c r="K63" s="50"/>
-      <c r="L63" s="50"/>
+      <c r="A63" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="48"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
+      <c r="L63" s="48"/>
     </row>
     <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A64" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B64" s="47"/>
       <c r="C64" s="47"/>
@@ -3903,7 +3798,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="3"/>
       <c r="H64" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I64" s="47"/>
       <c r="J64" s="47"/>
@@ -3912,16 +3807,16 @@
     </row>
     <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>0</v>
@@ -3929,16 +3824,16 @@
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>0</v>
@@ -3946,16 +3841,16 @@
     </row>
     <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A66" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="16">
+        <v>59</v>
+      </c>
+      <c r="D66" s="21">
         <v>63</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="E66" s="22" t="s">
         <v>1</v>
@@ -3963,19 +3858,19 @@
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
       <c r="H66" s="55" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="K66" s="21" t="s">
-        <v>47</v>
+        <v>12</v>
+      </c>
+      <c r="J66" s="16">
+        <v>35</v>
+      </c>
+      <c r="K66" s="21">
+        <v>23</v>
       </c>
       <c r="L66" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -3984,55 +3879,55 @@
         <v>2</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>39</v>
+        <v>3</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
       <c r="H67" s="55"/>
       <c r="I67" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="J67" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="J67" s="32">
+        <v>83</v>
+      </c>
+      <c r="K67" s="2">
+        <v>20</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A68" s="55"/>
       <c r="B68" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="28">
+        <v>26</v>
+      </c>
+      <c r="D68" s="21">
         <v>17</v>
       </c>
-      <c r="C68" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>45</v>
-      </c>
       <c r="E68" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
       <c r="H68" s="55"/>
       <c r="I68" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J68" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="K68" s="21" t="s">
-        <v>58</v>
+        <v>11</v>
+      </c>
+      <c r="J68" s="28">
+        <v>57</v>
+      </c>
+      <c r="K68" s="21">
+        <v>71</v>
       </c>
       <c r="L68" s="22" t="s">
         <v>1</v>
@@ -4041,16 +3936,16 @@
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A69" s="55"/>
       <c r="B69" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
+      </c>
+      <c r="C69" s="32">
+        <v>92</v>
+      </c>
+      <c r="D69" s="2">
+        <v>10</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
@@ -4059,25 +3954,25 @@
         <v>2</v>
       </c>
       <c r="J69" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>37</v>
+        <v>5</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1</v>
       </c>
       <c r="L69" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A70" s="56"/>
       <c r="B70" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C70" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>51</v>
+        <v>11</v>
+      </c>
+      <c r="C70" s="29">
+        <v>55</v>
+      </c>
+      <c r="D70" s="23">
+        <v>66</v>
       </c>
       <c r="E70" s="24" t="s">
         <v>1</v>
@@ -4086,47 +3981,47 @@
       <c r="G70" s="5"/>
       <c r="H70" s="56"/>
       <c r="I70" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70" s="23" t="s">
-        <v>44</v>
+        <v>12</v>
+      </c>
+      <c r="J70" s="29">
+        <v>36</v>
+      </c>
+      <c r="K70" s="23">
+        <v>15</v>
       </c>
       <c r="L70" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A71" s="53" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="D71" s="2">
+        <v>11</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
       <c r="H71" s="53" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="J71" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="J71" s="32">
+        <v>86</v>
+      </c>
+      <c r="K71" s="2">
+        <v>68</v>
       </c>
       <c r="L71" s="34" t="s">
         <v>1</v>
@@ -4135,28 +4030,28 @@
     <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A72" s="54"/>
       <c r="B72" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>46</v>
+        <v>12</v>
+      </c>
+      <c r="C72" s="16">
+        <v>32</v>
+      </c>
+      <c r="D72" s="21">
+        <v>22</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
       <c r="H72" s="54"/>
       <c r="I72" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K72" s="21" t="s">
-        <v>49</v>
+        <v>11</v>
+      </c>
+      <c r="J72" s="16">
+        <v>51</v>
+      </c>
+      <c r="K72" s="21">
+        <v>62</v>
       </c>
       <c r="L72" s="22" t="s">
         <v>1</v>
@@ -4165,16 +4060,16 @@
     <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A73" s="54"/>
       <c r="B73" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C73" s="32">
+        <v>84</v>
+      </c>
+      <c r="D73" s="2">
+        <v>31</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
@@ -4183,25 +4078,25 @@
         <v>2</v>
       </c>
       <c r="J73" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K73" s="2">
+        <v>3</v>
+      </c>
+      <c r="L73" s="34" t="s">
         <v>9</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L73" s="34" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A74" s="54"/>
       <c r="B74" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="C74" s="16">
+        <v>53</v>
+      </c>
+      <c r="D74" s="21">
+        <v>69</v>
       </c>
       <c r="E74" s="22" t="s">
         <v>1</v>
@@ -4210,16 +4105,16 @@
       <c r="G74" s="5"/>
       <c r="H74" s="54"/>
       <c r="I74" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K74" s="21" t="s">
-        <v>57</v>
+        <v>12</v>
+      </c>
+      <c r="J74" s="16">
+        <v>29</v>
+      </c>
+      <c r="K74" s="21">
+        <v>93</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -4228,28 +4123,28 @@
         <v>2</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D75" s="25">
+        <v>8</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
       <c r="H75" s="54"/>
       <c r="I75" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J75" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="K75" s="25" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="J75" s="20">
+        <v>94</v>
+      </c>
+      <c r="K75" s="25">
+        <v>18</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.15">
@@ -4281,24 +4176,24 @@
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
-      <c r="D78" s="50"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50"/>
-      <c r="I78" s="50"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="50"/>
-      <c r="L78" s="50"/>
+      <c r="A78" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="48"/>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
+      <c r="L78" s="48"/>
     </row>
     <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A79" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B79" s="47"/>
       <c r="C79" s="47"/>
@@ -4307,7 +4202,7 @@
       <c r="F79" s="2"/>
       <c r="G79" s="3"/>
       <c r="H79" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I79" s="47"/>
       <c r="J79" s="47"/>
@@ -4316,16 +4211,16 @@
     </row>
     <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>0</v>
@@ -4333,16 +4228,16 @@
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>0</v>
@@ -4350,36 +4245,36 @@
     </row>
     <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A81" s="57" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>55</v>
+        <v>11</v>
+      </c>
+      <c r="C81" s="16">
+        <v>59</v>
+      </c>
+      <c r="D81" s="21">
+        <v>92</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
       <c r="H81" s="55" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J81" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="K81" s="21" t="s">
-        <v>44</v>
+        <v>9</v>
+      </c>
+      <c r="J81" s="16">
+        <v>3</v>
+      </c>
+      <c r="K81" s="21">
+        <v>15</v>
       </c>
       <c r="L81" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -4388,10 +4283,10 @@
         <v>2</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D82" s="2">
+        <v>69</v>
       </c>
       <c r="E82" s="34" t="s">
         <v>1</v>
@@ -4400,61 +4295,61 @@
       <c r="G82" s="5"/>
       <c r="H82" s="55"/>
       <c r="I82" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>56</v>
+        <v>12</v>
+      </c>
+      <c r="J82" s="32">
+        <v>35</v>
+      </c>
+      <c r="K82" s="2">
+        <v>94</v>
       </c>
       <c r="L82" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="21" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A83" s="57"/>
       <c r="B83" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>47</v>
+        <v>9</v>
+      </c>
+      <c r="C83" s="28">
+        <v>10</v>
+      </c>
+      <c r="D83" s="21">
+        <v>23</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
       <c r="H83" s="55"/>
       <c r="I83" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J83" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K83" s="21" t="s">
-        <v>57</v>
+        <v>11</v>
+      </c>
+      <c r="J83" s="28">
+        <v>51</v>
+      </c>
+      <c r="K83" s="21">
+        <v>93</v>
       </c>
       <c r="L83" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A84" s="57"/>
       <c r="B84" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="C84" s="32">
+        <v>29</v>
+      </c>
+      <c r="D84" s="2">
+        <v>6</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
@@ -4463,10 +4358,10 @@
         <v>2</v>
       </c>
       <c r="J84" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="K84" s="2">
+        <v>62</v>
       </c>
       <c r="L84" s="34" t="s">
         <v>1</v>
@@ -4475,45 +4370,45 @@
     <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A85" s="58"/>
       <c r="B85" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D85" s="35" t="s">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="C85" s="27">
+        <v>55</v>
+      </c>
+      <c r="D85" s="35">
+        <v>86</v>
       </c>
       <c r="E85" s="36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
       <c r="H85" s="56"/>
       <c r="I85" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="J85" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="K85" s="23" t="s">
-        <v>45</v>
+        <v>9</v>
+      </c>
+      <c r="J85" s="29">
+        <v>1</v>
+      </c>
+      <c r="K85" s="23">
+        <v>17</v>
       </c>
       <c r="L85" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A86" s="51" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B86" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D86" s="37">
+        <v>68</v>
       </c>
       <c r="E86" s="38" t="s">
         <v>1</v>
@@ -4521,16 +4416,16 @@
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
       <c r="H86" s="53" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="I86" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="J86" s="32">
+        <v>32</v>
+      </c>
+      <c r="K86" s="2">
+        <v>63</v>
       </c>
       <c r="L86" s="34" t="s">
         <v>1</v>
@@ -4539,46 +4434,46 @@
     <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A87" s="52"/>
       <c r="B87" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="16">
         <v>11</v>
       </c>
-      <c r="C87" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D87" s="21" t="s">
-        <v>46</v>
+      <c r="D87" s="21">
+        <v>22</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
       <c r="H87" s="54"/>
       <c r="I87" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="K87" s="21" t="s">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="J87" s="16">
+        <v>57</v>
+      </c>
+      <c r="K87" s="21">
+        <v>83</v>
       </c>
       <c r="L87" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A88" s="52"/>
       <c r="B88" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="C88" s="32">
+        <v>31</v>
+      </c>
+      <c r="D88" s="2">
+        <v>18</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
@@ -4587,10 +4482,10 @@
         <v>2</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>58</v>
+        <v>5</v>
+      </c>
+      <c r="K88" s="2">
+        <v>71</v>
       </c>
       <c r="L88" s="34" t="s">
         <v>1</v>
@@ -4599,31 +4494,31 @@
     <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A89" s="52"/>
       <c r="B89" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D89" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="16">
         <v>53</v>
       </c>
+      <c r="D89" s="21">
+        <v>84</v>
+      </c>
       <c r="E89" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
       <c r="H89" s="54"/>
       <c r="I89" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="J89" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="K89" s="21" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="J89" s="16">
+        <v>8</v>
+      </c>
+      <c r="K89" s="21">
+        <v>36</v>
       </c>
       <c r="L89" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -4632,10 +4527,10 @@
         <v>2</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="25" t="s">
-        <v>51</v>
+        <v>7</v>
+      </c>
+      <c r="D90" s="25">
+        <v>66</v>
       </c>
       <c r="E90" s="26" t="s">
         <v>1</v>
@@ -4644,16 +4539,16 @@
       <c r="G90" s="5"/>
       <c r="H90" s="54"/>
       <c r="I90" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="K90" s="25" t="s">
-        <v>43</v>
+        <v>12</v>
+      </c>
+      <c r="J90" s="20">
+        <v>26</v>
+      </c>
+      <c r="K90" s="25">
+        <v>20</v>
       </c>
       <c r="L90" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4973,29 +4868,29 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="44"/>
-      <c r="B1" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
       <c r="B2" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
       <c r="E2" s="47"/>
       <c r="F2" s="3"/>
       <c r="G2" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H2" s="47"/>
       <c r="I2" s="47"/>
@@ -5007,10 +4902,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>0</v>
@@ -5020,152 +4915,152 @@
         <v>0</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
-        <v>59</v>
+      <c r="A4" s="49" t="s">
+        <v>24</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>11</v>
+      </c>
+      <c r="C4" s="16">
+        <v>57</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>50</v>
+        <v>9</v>
+      </c>
+      <c r="H4" s="16">
+        <v>10</v>
+      </c>
+      <c r="I4" s="21">
+        <v>63</v>
       </c>
       <c r="J4" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="48"/>
+      <c r="A5" s="49"/>
       <c r="B5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="C5" s="16">
+        <v>6</v>
+      </c>
+      <c r="D5" s="21">
+        <v>32</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="16">
         <v>15</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>53</v>
+      <c r="I5" s="21">
+        <v>84</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="48"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="16">
         <v>18</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>56</v>
+      <c r="D6" s="21">
+        <v>93</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="H6" s="16">
+        <v>51</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="16">
+        <v>59</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="16">
         <v>11</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>22</v>
+      <c r="I7" s="21">
+        <v>35</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="22" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
       <c r="B8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>49</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="18">
+        <v>8</v>
+      </c>
+      <c r="D8" s="23">
+        <v>62</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="29">
         <v>23</v>
       </c>
-      <c r="I8" s="23" t="s">
-        <v>58</v>
+      <c r="I8" s="23">
+        <v>71</v>
       </c>
       <c r="J8" s="24" t="s">
         <v>1</v>
@@ -5173,113 +5068,113 @@
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" s="20">
         <v>22</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>55</v>
+      <c r="D9" s="25">
+        <v>92</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="H9" s="20">
+        <v>1</v>
+      </c>
+      <c r="I9" s="25">
+        <v>29</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A10" s="46"/>
       <c r="B10" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="C10" s="16">
+        <v>53</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10" s="16">
         <v>17</v>
       </c>
-      <c r="I10" s="21" t="s">
-        <v>54</v>
+      <c r="I10" s="21">
+        <v>86</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A11" s="46"/>
       <c r="B11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+      <c r="C11" s="16">
+        <v>3</v>
+      </c>
+      <c r="D11" s="21">
+        <v>31</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>52</v>
+        <v>12</v>
+      </c>
+      <c r="H11" s="16">
+        <v>26</v>
+      </c>
+      <c r="I11" s="21">
+        <v>83</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="46"/>
       <c r="B12" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="16">
         <v>20</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>4</v>
+      <c r="D12" s="21">
+        <v>69</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="H12" s="16">
+        <v>94</v>
+      </c>
+      <c r="I12" s="21">
+        <v>66</v>
       </c>
       <c r="J12" s="22" t="s">
         <v>1</v>
@@ -5288,13 +5183,13 @@
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A13" s="46"/>
       <c r="B13" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="C13" s="16">
+        <v>55</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>2</v>
@@ -5303,14 +5198,14 @@
       <c r="G13" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>23</v>
+      <c r="H13" s="16">
+        <v>68</v>
+      </c>
+      <c r="I13" s="21">
+        <v>36</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -5327,29 +5222,29 @@
     </row>
     <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="50"/>
+      <c r="B15" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
       <c r="B16" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C16" s="47"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
       <c r="F16" s="3"/>
       <c r="G16" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H16" s="47"/>
       <c r="I16" s="47"/>
@@ -5361,10 +5256,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>0</v>
@@ -5374,83 +5269,83 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="48" t="s">
-        <v>61</v>
+      <c r="A18" s="49" t="s">
+        <v>26</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>40</v>
+        <v>11</v>
+      </c>
+      <c r="C18" s="27">
+        <v>59</v>
+      </c>
+      <c r="D18" s="21">
+        <v>8</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>52</v>
+        <v>8</v>
+      </c>
+      <c r="H18" s="16">
+        <v>83</v>
       </c>
       <c r="I18" s="39">
         <v>23</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="48"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="D19" s="21">
+        <v>29</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="H19" s="16">
+        <v>55</v>
+      </c>
+      <c r="I19" s="21">
+        <v>6</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="48"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" s="28">
         <v>22</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>3</v>
+      <c r="D20" s="21">
+        <v>68</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>1</v>
@@ -5460,66 +5355,66 @@
         <v>2</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>18</v>
+        <v>3</v>
+      </c>
+      <c r="I20" s="21">
+        <v>26</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="48"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="C21" s="16">
+        <v>93</v>
+      </c>
+      <c r="D21" s="21">
+        <v>3</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H21" s="16">
         <v>17</v>
       </c>
-      <c r="I21" s="21" t="s">
-        <v>49</v>
+      <c r="I21" s="21">
+        <v>62</v>
       </c>
       <c r="J21" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="C22" s="29">
+        <v>57</v>
+      </c>
+      <c r="D22" s="23">
+        <v>1</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="H22" s="29">
+        <v>84</v>
+      </c>
+      <c r="I22" s="23">
+        <v>69</v>
       </c>
       <c r="J22" s="24" t="s">
         <v>1</v>
@@ -5527,44 +5422,44 @@
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="25">
+        <v>32</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="H23" s="20">
+        <v>51</v>
+      </c>
+      <c r="I23" s="25">
+        <v>11</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A24" s="46"/>
       <c r="B24" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C24" s="16">
         <v>18</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>50</v>
+      <c r="D24" s="21">
+        <v>63</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>1</v>
@@ -5574,38 +5469,38 @@
         <v>2</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="I24" s="21">
+        <v>31</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A25" s="46"/>
       <c r="B25" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="C25" s="16">
+        <v>86</v>
+      </c>
+      <c r="D25" s="21">
+        <v>36</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H25" s="16">
         <v>15</v>
       </c>
-      <c r="I25" s="21" t="s">
-        <v>51</v>
+      <c r="I25" s="21">
+        <v>66</v>
       </c>
       <c r="J25" s="22" t="s">
         <v>1</v>
@@ -5614,29 +5509,29 @@
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A26" s="46"/>
       <c r="B26" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="C26" s="16">
+        <v>53</v>
+      </c>
+      <c r="D26" s="21">
+        <v>10</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="16">
         <v>20</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>57</v>
+      <c r="I26" s="21">
+        <v>94</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
@@ -5645,26 +5540,26 @@
         <v>2</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="D27" s="21">
+        <v>35</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H27" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>55</v>
+      <c r="H27" s="16">
+        <v>71</v>
+      </c>
+      <c r="I27" s="21">
+        <v>92</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -5681,29 +5576,29 @@
     </row>
     <row r="29" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
+      <c r="B29" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
       <c r="B30" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
       <c r="E30" s="47"/>
       <c r="F30" s="3"/>
       <c r="G30" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H30" s="47"/>
       <c r="I30" s="47"/>
@@ -5715,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>0</v>
@@ -5728,213 +5623,213 @@
         <v>0</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="48" t="s">
-        <v>66</v>
+      <c r="A32" s="49" t="s">
+        <v>31</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="C32" s="27">
+        <v>59</v>
+      </c>
+      <c r="D32" s="35">
+        <v>29</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="H32" s="16">
+        <v>8</v>
+      </c>
+      <c r="I32" s="21">
+        <v>92</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="48"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D33" s="21">
         <v>23</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H33" s="32" t="s">
-        <v>50</v>
+      <c r="H33" s="32">
+        <v>63</v>
       </c>
       <c r="I33" s="2">
         <v>17</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A34" s="48"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="49"/>
       <c r="B34" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>9</v>
+      </c>
+      <c r="C34" s="31">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>84</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="28">
+        <v>53</v>
+      </c>
+      <c r="I34" s="21">
         <v>35</v>
       </c>
-      <c r="I34" s="21" t="s">
-        <v>22</v>
-      </c>
       <c r="J34" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="48"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>42</v>
+      <c r="C35" s="16">
+        <v>69</v>
+      </c>
+      <c r="D35" s="21">
+        <v>11</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H35" s="32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I35" s="2">
         <v>22</v>
       </c>
       <c r="J35" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="49"/>
+      <c r="B36" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="29">
+        <v>51</v>
+      </c>
+      <c r="D36" s="23">
+        <v>36</v>
+      </c>
+      <c r="E36" s="24" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="48"/>
-      <c r="B36" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>17</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>54</v>
+        <v>9</v>
+      </c>
+      <c r="H36" s="29">
+        <v>6</v>
+      </c>
+      <c r="I36" s="23">
+        <v>86</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37" s="25">
         <v>15</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="H37" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>56</v>
+      <c r="H37" s="20">
+        <v>68</v>
+      </c>
+      <c r="I37" s="25">
+        <v>93</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A38" s="46"/>
       <c r="B38" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>57</v>
+        <v>9</v>
+      </c>
+      <c r="C38" s="32">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2">
+        <v>94</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="H38" s="32">
+        <v>57</v>
+      </c>
+      <c r="I38" s="2">
+        <v>31</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
@@ -5942,52 +5837,52 @@
       <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>18</v>
+      <c r="C39" s="16">
+        <v>71</v>
+      </c>
+      <c r="D39" s="21">
+        <v>26</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="14" t="s">
         <v>2</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I39" s="21">
         <v>18</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A40" s="46"/>
       <c r="B40" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="C40" s="32">
+        <v>55</v>
+      </c>
+      <c r="D40" s="2">
+        <v>32</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I40" s="21" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="H40" s="16">
+        <v>3</v>
+      </c>
+      <c r="I40" s="21">
+        <v>66</v>
       </c>
       <c r="J40" s="22" t="s">
         <v>1</v>
@@ -5999,23 +5894,23 @@
         <v>2</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" s="21">
         <v>20</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="H41" s="20">
+        <v>83</v>
+      </c>
+      <c r="I41" s="25">
+        <v>62</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>1</v>
@@ -6035,29 +5930,29 @@
     </row>
     <row r="43" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
-      <c r="B43" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
+      <c r="B43" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
       <c r="B44" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C44" s="47"/>
       <c r="D44" s="47"/>
       <c r="E44" s="47"/>
       <c r="F44" s="3"/>
       <c r="G44" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H44" s="47"/>
       <c r="I44" s="47"/>
@@ -6069,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>0</v>
@@ -6082,152 +5977,152 @@
         <v>0</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="48" t="s">
-        <v>68</v>
+      <c r="A46" s="49" t="s">
+        <v>33</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="C46" s="16">
+        <v>53</v>
       </c>
       <c r="D46" s="21">
         <v>20</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I46" s="21" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="H46" s="16">
+        <v>3</v>
+      </c>
+      <c r="I46" s="21">
+        <v>36</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="48"/>
+      <c r="A47" s="49"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>57</v>
+        <v>3</v>
+      </c>
+      <c r="D47" s="2">
+        <v>94</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="H47" s="32">
+        <v>84</v>
+      </c>
+      <c r="I47" s="2">
+        <v>63</v>
       </c>
       <c r="J47" s="34" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A48" s="48"/>
+    <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A48" s="49"/>
       <c r="B48" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="28">
         <v>11</v>
       </c>
-      <c r="C48" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>3</v>
+      <c r="D48" s="21">
+        <v>68</v>
       </c>
       <c r="E48" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="28" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="H48" s="28">
+        <v>51</v>
       </c>
       <c r="I48" s="21">
         <v>15</v>
       </c>
       <c r="J48" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A49" s="49"/>
+      <c r="B49" s="30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="48"/>
-      <c r="B49" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>40</v>
+      <c r="C49" s="32">
+        <v>26</v>
+      </c>
+      <c r="D49" s="2">
+        <v>8</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H49" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>54</v>
+        <v>6</v>
+      </c>
+      <c r="I49" s="2">
+        <v>86</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="49"/>
+      <c r="A50" s="50"/>
       <c r="B50" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="29" t="s">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="C50" s="29">
+        <v>55</v>
       </c>
       <c r="D50" s="23">
         <v>17</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="H50" s="29">
+        <v>6</v>
+      </c>
+      <c r="I50" s="23">
+        <v>66</v>
       </c>
       <c r="J50" s="24" t="s">
         <v>1</v>
@@ -6235,29 +6130,29 @@
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A51" s="46" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="D51" s="2">
+        <v>92</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="H51" s="32">
+        <v>31</v>
+      </c>
+      <c r="I51" s="2">
+        <v>62</v>
       </c>
       <c r="J51" s="34" t="s">
         <v>1</v>
@@ -6266,85 +6161,85 @@
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A52" s="46"/>
       <c r="B52" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C52" s="16">
+        <v>1</v>
+      </c>
+      <c r="D52" s="21">
+        <v>71</v>
       </c>
       <c r="E52" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="16" t="s">
-        <v>48</v>
+        <v>11</v>
+      </c>
+      <c r="H52" s="16">
+        <v>57</v>
       </c>
       <c r="I52" s="21">
         <v>23</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A53" s="46"/>
       <c r="B53" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C53" s="32">
+        <v>29</v>
       </c>
       <c r="D53" s="2">
         <v>22</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H53" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>56</v>
+        <v>7</v>
+      </c>
+      <c r="I53" s="2">
+        <v>93</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A54" s="46"/>
       <c r="B54" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C54" s="16">
+        <v>59</v>
       </c>
       <c r="D54" s="21">
         <v>18</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="H54" s="16">
+        <v>10</v>
+      </c>
+      <c r="I54" s="21">
+        <v>32</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
@@ -6353,23 +6248,23 @@
         <v>2</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>52</v>
+        <v>4</v>
+      </c>
+      <c r="D55" s="25">
+        <v>83</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="25" t="s">
-        <v>4</v>
+        <v>12</v>
+      </c>
+      <c r="H55" s="20">
+        <v>35</v>
+      </c>
+      <c r="I55" s="25">
+        <v>69</v>
       </c>
       <c r="J55" s="26" t="s">
         <v>1</v>
@@ -6389,29 +6284,29 @@
     </row>
     <row r="57" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
-      <c r="B57" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="50"/>
-      <c r="J57" s="50"/>
+      <c r="B57" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
       <c r="B58" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C58" s="47"/>
       <c r="D58" s="47"/>
       <c r="E58" s="47"/>
       <c r="F58" s="3"/>
       <c r="G58" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H58" s="47"/>
       <c r="I58" s="47"/>
@@ -6423,10 +6318,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>0</v>
@@ -6436,182 +6331,182 @@
         <v>0</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="16">
+        <v>59</v>
+      </c>
+      <c r="D60" s="21">
         <v>63</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="E60" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="H60" s="16">
+        <v>35</v>
       </c>
       <c r="I60" s="21">
         <v>23</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="48"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>39</v>
+        <v>3</v>
+      </c>
+      <c r="D61" s="2">
+        <v>6</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>52</v>
+        <v>8</v>
+      </c>
+      <c r="H61" s="32">
+        <v>83</v>
       </c>
       <c r="I61" s="2">
         <v>20</v>
       </c>
       <c r="J61" s="34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A62" s="49"/>
+      <c r="B62" s="14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A62" s="48"/>
-      <c r="B62" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="28" t="s">
-        <v>18</v>
+      <c r="C62" s="28">
+        <v>26</v>
       </c>
       <c r="D62" s="21">
         <v>17</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="I62" s="21" t="s">
-        <v>58</v>
+        <v>11</v>
+      </c>
+      <c r="H62" s="28">
+        <v>57</v>
+      </c>
+      <c r="I62" s="21">
+        <v>71</v>
       </c>
       <c r="J62" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="48"/>
+      <c r="A63" s="49"/>
       <c r="B63" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
+      </c>
+      <c r="C63" s="32">
+        <v>92</v>
+      </c>
+      <c r="D63" s="2">
+        <v>10</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H63" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>37</v>
+        <v>5</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
       </c>
       <c r="J63" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="49"/>
+      <c r="B64" s="17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="48"/>
-      <c r="B64" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>51</v>
+      <c r="C64" s="29">
+        <v>55</v>
+      </c>
+      <c r="D64" s="23">
+        <v>66</v>
       </c>
       <c r="E64" s="24" t="s">
         <v>1</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="H64" s="29">
+        <v>36</v>
       </c>
       <c r="I64" s="23">
         <v>15</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A65" s="45" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="D65" s="2">
+        <v>11</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="H65" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="H65" s="32">
+        <v>86</v>
+      </c>
+      <c r="I65" s="2">
+        <v>68</v>
       </c>
       <c r="J65" s="34" t="s">
         <v>1</v>
@@ -6620,26 +6515,26 @@
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A66" s="46"/>
       <c r="B66" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="C66" s="16">
+        <v>32</v>
       </c>
       <c r="D66" s="21">
         <v>22</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" s="21" t="s">
-        <v>49</v>
+        <v>11</v>
+      </c>
+      <c r="H66" s="16">
+        <v>51</v>
+      </c>
+      <c r="I66" s="21">
+        <v>62</v>
       </c>
       <c r="J66" s="22" t="s">
         <v>1</v>
@@ -6648,57 +6543,57 @@
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A67" s="46"/>
       <c r="B67" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="C67" s="32">
+        <v>84</v>
+      </c>
+      <c r="D67" s="2">
+        <v>31</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H67" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" s="2">
+        <v>3</v>
+      </c>
+      <c r="J67" s="34" t="s">
         <v>9</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J67" s="34" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A68" s="46"/>
       <c r="B68" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="C68" s="16">
+        <v>53</v>
+      </c>
+      <c r="D68" s="21">
+        <v>69</v>
       </c>
       <c r="E68" s="22" t="s">
         <v>1</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="21" t="s">
-        <v>56</v>
+        <v>12</v>
+      </c>
+      <c r="H68" s="16">
+        <v>29</v>
+      </c>
+      <c r="I68" s="21">
+        <v>93</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
@@ -6707,26 +6602,26 @@
         <v>2</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>40</v>
+        <v>6</v>
+      </c>
+      <c r="D69" s="25">
+        <v>8</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H69" s="20" t="s">
-        <v>57</v>
+        <v>8</v>
+      </c>
+      <c r="H69" s="20">
+        <v>94</v>
       </c>
       <c r="I69" s="25">
         <v>18</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -6743,29 +6638,29 @@
     </row>
     <row r="71" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A71" s="44"/>
-      <c r="B71" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
-      <c r="J71" s="50"/>
+      <c r="B71" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
       <c r="B72" s="47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C72" s="47"/>
       <c r="D72" s="47"/>
       <c r="E72" s="47"/>
       <c r="F72" s="3"/>
       <c r="G72" s="47" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H72" s="47"/>
       <c r="I72" s="47"/>
@@ -6777,10 +6672,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>0</v>
@@ -6790,182 +6685,182 @@
         <v>0</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="48" t="s">
-        <v>65</v>
+      <c r="A74" s="49" t="s">
+        <v>30</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>55</v>
+        <v>11</v>
+      </c>
+      <c r="C74" s="16">
+        <v>59</v>
+      </c>
+      <c r="D74" s="21">
+        <v>92</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H74" s="16" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="H74" s="16">
+        <v>3</v>
       </c>
       <c r="I74" s="21">
         <v>15</v>
       </c>
       <c r="J74" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
+      <c r="A75" s="49"/>
       <c r="B75" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D75" s="2">
+        <v>69</v>
       </c>
       <c r="E75" s="34" t="s">
         <v>1</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="H75" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
+      </c>
+      <c r="H75" s="32">
+        <v>35</v>
+      </c>
+      <c r="I75" s="2">
+        <v>94</v>
       </c>
       <c r="J75" s="34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="21" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A76" s="49"/>
       <c r="B76" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>41</v>
+        <v>9</v>
+      </c>
+      <c r="C76" s="28">
+        <v>10</v>
       </c>
       <c r="D76" s="21">
         <v>23</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" s="21" t="s">
-        <v>56</v>
+        <v>11</v>
+      </c>
+      <c r="H76" s="28">
+        <v>51</v>
+      </c>
+      <c r="I76" s="21">
+        <v>93</v>
       </c>
       <c r="J76" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="48"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="C77" s="32">
+        <v>29</v>
+      </c>
+      <c r="D77" s="2">
+        <v>6</v>
       </c>
       <c r="E77" s="34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H77" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="I77" s="2">
+        <v>62</v>
       </c>
       <c r="J77" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="49"/>
+      <c r="A78" s="50"/>
       <c r="B78" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D78" s="35" t="s">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="C78" s="27">
+        <v>55</v>
+      </c>
+      <c r="D78" s="35">
+        <v>86</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="29" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="H78" s="29">
+        <v>1</v>
       </c>
       <c r="I78" s="23">
         <v>17</v>
       </c>
       <c r="J78" s="24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A79" s="46" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="37" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D79" s="37">
+        <v>68</v>
       </c>
       <c r="E79" s="38" t="s">
         <v>1</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="H79" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="H79" s="32">
+        <v>32</v>
+      </c>
+      <c r="I79" s="2">
+        <v>63</v>
       </c>
       <c r="J79" s="34" t="s">
         <v>1</v>
@@ -6974,54 +6869,54 @@
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A80" s="46"/>
       <c r="B80" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="16">
         <v>11</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>42</v>
       </c>
       <c r="D80" s="21">
         <v>22</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="H80" s="16">
+        <v>57</v>
+      </c>
+      <c r="I80" s="21">
+        <v>83</v>
       </c>
       <c r="J80" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A81" s="46"/>
       <c r="B81" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="32" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="C81" s="32">
+        <v>31</v>
       </c>
       <c r="D81" s="2">
         <v>18</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="30" t="s">
         <v>2</v>
       </c>
       <c r="H81" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>58</v>
+        <v>5</v>
+      </c>
+      <c r="I81" s="2">
+        <v>71</v>
       </c>
       <c r="J81" s="34" t="s">
         <v>1</v>
@@ -7030,29 +6925,29 @@
     <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A82" s="46"/>
       <c r="B82" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D82" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="16">
         <v>53</v>
       </c>
+      <c r="D82" s="21">
+        <v>84</v>
+      </c>
       <c r="E82" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I82" s="21" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="H82" s="16">
+        <v>8</v>
+      </c>
+      <c r="I82" s="21">
+        <v>36</v>
       </c>
       <c r="J82" s="22" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
@@ -7061,26 +6956,26 @@
         <v>2</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="25" t="s">
-        <v>51</v>
+        <v>7</v>
+      </c>
+      <c r="D83" s="25">
+        <v>66</v>
       </c>
       <c r="E83" s="26" t="s">
         <v>1</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H83" s="20" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="H83" s="20">
+        <v>26</v>
       </c>
       <c r="I83" s="25">
         <v>20</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7095,8 +6990,6 @@
     <mergeCell ref="A65:A69"/>
     <mergeCell ref="B72:E72"/>
     <mergeCell ref="B71:J71"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G16:J16"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="G30:J30"/>
@@ -7109,12 +7002,14 @@
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="A23:A27"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A4:A8"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A4:A8"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C14 B18:C28 B32:C42 B46:C56 B60:C70 B74:C83">
     <cfRule type="expression" dxfId="27" priority="50">
@@ -7213,11 +7108,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f8e6109263404e4da1831cd151bd9fd5>
+    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </kd8ebdb17ae1461db4d8c38e130fcffb>
+    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -7464,7 +7377,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7473,25 +7386,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f8e6109263404e4da1831cd151bd9fd5>
-    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </kd8ebdb17ae1461db4d8c38e130fcffb>
-    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -7499,7 +7411,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7518,27 +7430,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MIO_Spielplan.xlsx
+++ b/MIO_Spielplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D608115-CF13-9149-BBCF-22F4E272B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A2C549-82E9-B446-A0AD-BED539AAFACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="32">
   <si>
     <t>Klasse</t>
   </si>
@@ -49,18 +49,6 @@
   </si>
   <si>
     <t>73|74</t>
-  </si>
-  <si>
-    <t>75|76</t>
-  </si>
-  <si>
-    <t>77|78</t>
-  </si>
-  <si>
-    <t>79|80</t>
-  </si>
-  <si>
-    <t>81|82</t>
   </si>
   <si>
     <t>2f</t>
@@ -709,17 +697,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -727,10 +709,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -743,6 +725,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2155,51 +2143,51 @@
       <c r="L1" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
+      <c r="A3" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
+      <c r="A4" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
       <c r="F4" s="2"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="H4" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>0</v>
@@ -2207,16 +2195,16 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>0</v>
@@ -2224,28 +2212,28 @@
       <c r="N5" s="40"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="55" t="s">
-        <v>24</v>
+      <c r="A6" s="53" t="s">
+        <v>20</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C6" s="16">
         <v>57</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>7</v>
+      <c r="D6" s="21">
+        <v>82</v>
       </c>
       <c r="E6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="55" t="s">
-        <v>24</v>
+      <c r="H6" s="53" t="s">
+        <v>20</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J6" s="16">
         <v>10</v>
@@ -2258,9 +2246,9 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="55"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C7" s="16">
         <v>6</v>
@@ -2269,13 +2257,13 @@
         <v>32</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="55"/>
+      <c r="H7" s="53"/>
       <c r="I7" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" s="16">
         <v>15</v>
@@ -2284,13 +2272,13 @@
         <v>84</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A8" s="55"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8" s="16">
         <v>18</v>
@@ -2299,28 +2287,28 @@
         <v>93</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="55"/>
+      <c r="H8" s="53"/>
       <c r="I8" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J8" s="16">
         <v>51</v>
       </c>
-      <c r="K8" s="21" t="s">
-        <v>6</v>
+      <c r="K8" s="21">
+        <v>80</v>
       </c>
       <c r="L8" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A9" s="55"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C9" s="16">
         <v>59</v>
@@ -2333,9 +2321,9 @@
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="55"/>
+      <c r="H9" s="53"/>
       <c r="I9" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J9" s="16">
         <v>11</v>
@@ -2344,13 +2332,13 @@
         <v>35</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" s="18">
         <v>8</v>
@@ -2363,9 +2351,9 @@
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="56"/>
+      <c r="H10" s="54"/>
       <c r="I10" s="17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J10" s="29">
         <v>23</v>
@@ -2378,11 +2366,11 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="53" t="s">
-        <v>25</v>
+      <c r="A11" s="51" t="s">
+        <v>21</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11" s="20">
         <v>22</v>
@@ -2391,15 +2379,15 @@
         <v>92</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="53" t="s">
-        <v>25</v>
+      <c r="H11" s="51" t="s">
+        <v>21</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J11" s="20">
         <v>1</v>
@@ -2408,28 +2396,28 @@
         <v>29</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A12" s="54"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12" s="16">
         <v>53</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>5</v>
+      <c r="D12" s="21">
+        <v>77</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="54"/>
+      <c r="H12" s="52"/>
       <c r="I12" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12" s="16">
         <v>17</v>
@@ -2438,13 +2426,13 @@
         <v>86</v>
       </c>
       <c r="L12" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="54"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C13" s="16">
         <v>3</v>
@@ -2453,13 +2441,13 @@
         <v>31</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="54"/>
+      <c r="H13" s="52"/>
       <c r="I13" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J13" s="16">
         <v>26</v>
@@ -2468,13 +2456,13 @@
         <v>83</v>
       </c>
       <c r="L13" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A14" s="54"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C14" s="16">
         <v>20</v>
@@ -2487,9 +2475,9 @@
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="54"/>
+      <c r="H14" s="52"/>
       <c r="I14" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J14" s="16">
         <v>94</v>
@@ -2502,22 +2490,22 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A15" s="54"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" s="16">
         <v>55</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>4</v>
+      <c r="D15" s="21">
+        <v>75</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="54"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
@@ -2528,7 +2516,7 @@
         <v>36</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.15">
@@ -2560,51 +2548,51 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="48"/>
+      <c r="A18" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
     </row>
     <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A19" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
+      <c r="A19" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
+      <c r="H19" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>0</v>
@@ -2612,27 +2600,27 @@
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A21" s="55" t="s">
-        <v>26</v>
+      <c r="A21" s="53" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C21" s="27">
         <v>59</v>
@@ -2641,15 +2629,15 @@
         <v>8</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="55" t="s">
-        <v>26</v>
+      <c r="H21" s="53" t="s">
+        <v>22</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J21" s="16">
         <v>83</v>
@@ -2658,28 +2646,28 @@
         <v>23</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="55"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>4</v>
+      <c r="C22" s="16">
+        <v>75</v>
       </c>
       <c r="D22" s="21">
         <v>29</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="55"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J22" s="16">
         <v>55</v>
@@ -2688,13 +2676,13 @@
         <v>6</v>
       </c>
       <c r="L22" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A23" s="55"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C23" s="28">
         <v>22</v>
@@ -2707,7 +2695,7 @@
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="55"/>
+      <c r="H23" s="53"/>
       <c r="I23" s="14" t="s">
         <v>2</v>
       </c>
@@ -2718,13 +2706,13 @@
         <v>26</v>
       </c>
       <c r="L23" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A24" s="55"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C24" s="16">
         <v>93</v>
@@ -2733,13 +2721,13 @@
         <v>3</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="55"/>
+      <c r="H24" s="53"/>
       <c r="I24" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J24" s="16">
         <v>17</v>
@@ -2752,9 +2740,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="56"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C25" s="29">
         <v>57</v>
@@ -2763,13 +2751,13 @@
         <v>1</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="56"/>
+      <c r="H25" s="54"/>
       <c r="I25" s="17" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J25" s="29">
         <v>84</v>
@@ -2782,28 +2770,28 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="53" t="s">
-        <v>27</v>
+      <c r="A26" s="51" t="s">
+        <v>23</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>7</v>
+      <c r="C26" s="20">
+        <v>82</v>
       </c>
       <c r="D26" s="25">
         <v>32</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="53" t="s">
-        <v>27</v>
+      <c r="H26" s="51" t="s">
+        <v>23</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J26" s="20">
         <v>51</v>
@@ -2812,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A27" s="54"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="16">
         <v>18</v>
@@ -2831,24 +2819,24 @@
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="54"/>
+      <c r="H27" s="52"/>
       <c r="I27" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J27" s="16" t="s">
-        <v>6</v>
+      <c r="J27" s="16">
+        <v>80</v>
       </c>
       <c r="K27" s="21">
         <v>31</v>
       </c>
       <c r="L27" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="54"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C28" s="16">
         <v>86</v>
@@ -2857,13 +2845,13 @@
         <v>36</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="54"/>
+      <c r="H28" s="52"/>
       <c r="I28" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J28" s="16">
         <v>15</v>
@@ -2876,9 +2864,9 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A29" s="54"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C29" s="16">
         <v>53</v>
@@ -2887,13 +2875,13 @@
         <v>10</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="54"/>
+      <c r="H29" s="52"/>
       <c r="I29" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J29" s="16">
         <v>20</v>
@@ -2902,26 +2890,26 @@
         <v>94</v>
       </c>
       <c r="L29" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A30" s="54"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>5</v>
+      <c r="C30" s="16">
+        <v>77</v>
       </c>
       <c r="D30" s="21">
         <v>35</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="54"/>
+      <c r="H30" s="52"/>
       <c r="I30" s="14" t="s">
         <v>1</v>
       </c>
@@ -2932,7 +2920,7 @@
         <v>92</v>
       </c>
       <c r="L30" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.15">
@@ -2964,51 +2952,51 @@
       <c r="L32" s="7"/>
     </row>
     <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
+      <c r="A33" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
     </row>
     <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
+      <c r="A34" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
+      <c r="H34" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
     </row>
     <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>0</v>
@@ -3016,27 +3004,27 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K35" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A36" s="55" t="s">
-        <v>31</v>
+      <c r="A36" s="53" t="s">
+        <v>27</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C36" s="27">
         <v>59</v>
@@ -3045,15 +3033,15 @@
         <v>29</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="55" t="s">
-        <v>31</v>
+      <c r="H36" s="53" t="s">
+        <v>27</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="16">
         <v>8</v>
@@ -3062,26 +3050,26 @@
         <v>92</v>
       </c>
       <c r="L36" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="55"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>5</v>
+      <c r="C37" s="16">
+        <v>77</v>
       </c>
       <c r="D37" s="21">
         <v>23</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="55"/>
+      <c r="H37" s="53"/>
       <c r="I37" s="30" t="s">
         <v>1</v>
       </c>
@@ -3092,13 +3080,13 @@
         <v>17</v>
       </c>
       <c r="L37" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A38" s="55"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C38" s="31">
         <v>1</v>
@@ -3107,13 +3095,13 @@
         <v>84</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="55"/>
+      <c r="H38" s="53"/>
       <c r="I38" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J38" s="28">
         <v>53</v>
@@ -3122,11 +3110,11 @@
         <v>35</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A39" s="55"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
@@ -3137,28 +3125,28 @@
         <v>11</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="55"/>
+      <c r="H39" s="53"/>
       <c r="I39" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J39" s="32" t="s">
-        <v>4</v>
+      <c r="J39" s="32">
+        <v>75</v>
       </c>
       <c r="K39" s="2">
         <v>22</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="56"/>
+      <c r="A40" s="54"/>
       <c r="B40" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C40" s="29">
         <v>51</v>
@@ -3167,13 +3155,13 @@
         <v>36</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="56"/>
+      <c r="H40" s="54"/>
       <c r="I40" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J40" s="29">
         <v>6</v>
@@ -3182,29 +3170,29 @@
         <v>86</v>
       </c>
       <c r="L40" s="24" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="53" t="s">
-        <v>32</v>
+      <c r="A41" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="20" t="s">
-        <v>6</v>
+      <c r="C41" s="20">
+        <v>80</v>
       </c>
       <c r="D41" s="25">
         <v>15</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="53" t="s">
-        <v>32</v>
+      <c r="H41" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>1</v>
@@ -3216,13 +3204,13 @@
         <v>93</v>
       </c>
       <c r="L41" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="54"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C42" s="32">
         <v>10</v>
@@ -3231,13 +3219,13 @@
         <v>94</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="54"/>
+      <c r="H42" s="52"/>
       <c r="I42" s="30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J42" s="32">
         <v>57</v>
@@ -3246,11 +3234,11 @@
         <v>31</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="54"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="14" t="s">
         <v>1</v>
       </c>
@@ -3261,28 +3249,28 @@
         <v>26</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="54"/>
+      <c r="H43" s="52"/>
       <c r="I43" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J43" s="16" t="s">
-        <v>7</v>
+      <c r="J43" s="16">
+        <v>82</v>
       </c>
       <c r="K43" s="21">
         <v>18</v>
       </c>
       <c r="L43" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A44" s="54"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C44" s="32">
         <v>55</v>
@@ -3291,13 +3279,13 @@
         <v>32</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="54"/>
+      <c r="H44" s="52"/>
       <c r="I44" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J44" s="16">
         <v>3</v>
@@ -3310,7 +3298,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A45" s="54"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="14" t="s">
         <v>2</v>
       </c>
@@ -3321,13 +3309,13 @@
         <v>20</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="54"/>
+      <c r="H45" s="52"/>
       <c r="I45" s="19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J45" s="20">
         <v>83</v>
@@ -3368,51 +3356,51 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
-      <c r="L48" s="48"/>
+      <c r="A48" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
+      <c r="A49" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
       <c r="F49" s="2"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
+      <c r="H49" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
     </row>
     <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>0</v>
@@ -3420,27 +3408,27 @@
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
       <c r="H50" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I50" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A51" s="55" t="s">
-        <v>33</v>
+      <c r="A51" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C51" s="16">
         <v>53</v>
@@ -3449,15 +3437,15 @@
         <v>20</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="55" t="s">
-        <v>33</v>
+      <c r="H51" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J51" s="16">
         <v>3</v>
@@ -3466,11 +3454,11 @@
         <v>36</v>
       </c>
       <c r="L51" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="55"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="30" t="s">
         <v>2</v>
       </c>
@@ -3481,13 +3469,13 @@
         <v>94</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="55"/>
+      <c r="H52" s="53"/>
       <c r="I52" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J52" s="32">
         <v>84</v>
@@ -3500,9 +3488,9 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A53" s="55"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C53" s="28">
         <v>11</v>
@@ -3515,9 +3503,9 @@
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="55"/>
+      <c r="H53" s="53"/>
       <c r="I53" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J53" s="28">
         <v>51</v>
@@ -3526,13 +3514,13 @@
         <v>15</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A54" s="55"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C54" s="32">
         <v>26</v>
@@ -3541,28 +3529,28 @@
         <v>8</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="55"/>
+      <c r="H54" s="53"/>
       <c r="I54" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="32" t="s">
-        <v>6</v>
+      <c r="J54" s="32">
+        <v>80</v>
       </c>
       <c r="K54" s="2">
         <v>86</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="56"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C55" s="29">
         <v>55</v>
@@ -3571,13 +3559,13 @@
         <v>17</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="56"/>
+      <c r="H55" s="54"/>
       <c r="I55" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J55" s="29">
         <v>6</v>
@@ -3590,28 +3578,28 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="53" t="s">
-        <v>34</v>
+      <c r="A56" s="51" t="s">
+        <v>30</v>
       </c>
       <c r="B56" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="32" t="s">
-        <v>5</v>
+      <c r="C56" s="32">
+        <v>77</v>
       </c>
       <c r="D56" s="2">
         <v>92</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="53" t="s">
-        <v>34</v>
+      <c r="H56" s="51" t="s">
+        <v>30</v>
       </c>
       <c r="I56" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J56" s="32">
         <v>31</v>
@@ -3624,9 +3612,9 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A57" s="54"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C57" s="16">
         <v>1</v>
@@ -3639,9 +3627,9 @@
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="54"/>
+      <c r="H57" s="52"/>
       <c r="I57" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J57" s="16">
         <v>57</v>
@@ -3650,13 +3638,13 @@
         <v>23</v>
       </c>
       <c r="L57" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="54"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C58" s="32">
         <v>29</v>
@@ -3665,28 +3653,28 @@
         <v>22</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="54"/>
+      <c r="H58" s="52"/>
       <c r="I58" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J58" s="32" t="s">
-        <v>7</v>
+      <c r="J58" s="32">
+        <v>82</v>
       </c>
       <c r="K58" s="2">
         <v>93</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A59" s="54"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C59" s="16">
         <v>59</v>
@@ -3695,13 +3683,13 @@
         <v>18</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="54"/>
+      <c r="H59" s="52"/>
       <c r="I59" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J59" s="16">
         <v>10</v>
@@ -3710,28 +3698,28 @@
         <v>32</v>
       </c>
       <c r="L59" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A60" s="54"/>
+      <c r="A60" s="52"/>
       <c r="B60" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="20" t="s">
-        <v>4</v>
+      <c r="C60" s="20">
+        <v>75</v>
       </c>
       <c r="D60" s="25">
         <v>83</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="54"/>
+      <c r="H60" s="52"/>
       <c r="I60" s="19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J60" s="20">
         <v>35</v>
@@ -3772,51 +3760,51 @@
       <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
-      <c r="D63" s="48"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
-      <c r="L63" s="48"/>
+      <c r="A63" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="45"/>
     </row>
     <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" s="47"/>
-      <c r="C64" s="47"/>
-      <c r="D64" s="47"/>
-      <c r="E64" s="47"/>
+      <c r="A64" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="46"/>
       <c r="F64" s="2"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="47"/>
-      <c r="J64" s="47"/>
-      <c r="K64" s="47"/>
-      <c r="L64" s="47"/>
+      <c r="H64" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" s="46"/>
+      <c r="J64" s="46"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="46"/>
     </row>
     <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>0</v>
@@ -3824,27 +3812,27 @@
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
       <c r="H65" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I65" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L65" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A66" s="55" t="s">
-        <v>28</v>
+      <c r="A66" s="53" t="s">
+        <v>24</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C66" s="16">
         <v>59</v>
@@ -3857,11 +3845,11 @@
       </c>
       <c r="F66" s="4"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="55" t="s">
-        <v>28</v>
+      <c r="H66" s="53" t="s">
+        <v>24</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J66" s="16">
         <v>35</v>
@@ -3870,11 +3858,11 @@
         <v>23</v>
       </c>
       <c r="L66" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="55"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="30" t="s">
         <v>2</v>
       </c>
@@ -3885,13 +3873,13 @@
         <v>6</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F67" s="4"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="55"/>
+      <c r="H67" s="53"/>
       <c r="I67" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J67" s="32">
         <v>83</v>
@@ -3900,13 +3888,13 @@
         <v>20</v>
       </c>
       <c r="L67" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A68" s="55"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C68" s="28">
         <v>26</v>
@@ -3915,13 +3903,13 @@
         <v>17</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="55"/>
+      <c r="H68" s="53"/>
       <c r="I68" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J68" s="28">
         <v>57</v>
@@ -3934,9 +3922,9 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A69" s="55"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C69" s="32">
         <v>92</v>
@@ -3945,28 +3933,28 @@
         <v>10</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="55"/>
+      <c r="H69" s="53"/>
       <c r="I69" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J69" s="32" t="s">
+      <c r="J69" s="32">
+        <v>77</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1</v>
+      </c>
+      <c r="L69" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="K69" s="2">
-        <v>1</v>
-      </c>
-      <c r="L69" s="34" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="56"/>
+      <c r="A70" s="54"/>
       <c r="B70" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C70" s="29">
         <v>55</v>
@@ -3979,9 +3967,9 @@
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="56"/>
+      <c r="H70" s="54"/>
       <c r="I70" s="17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J70" s="29">
         <v>36</v>
@@ -3990,32 +3978,32 @@
         <v>15</v>
       </c>
       <c r="L70" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="53" t="s">
-        <v>35</v>
+      <c r="A71" s="51" t="s">
+        <v>31</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="32" t="s">
-        <v>4</v>
+      <c r="C71" s="32">
+        <v>75</v>
       </c>
       <c r="D71" s="2">
         <v>11</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="53" t="s">
-        <v>35</v>
+      <c r="H71" s="51" t="s">
+        <v>31</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J71" s="32">
         <v>86</v>
@@ -4028,9 +4016,9 @@
       </c>
     </row>
     <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A72" s="54"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C72" s="16">
         <v>32</v>
@@ -4039,13 +4027,13 @@
         <v>22</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="54"/>
+      <c r="H72" s="52"/>
       <c r="I72" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J72" s="16">
         <v>51</v>
@@ -4058,9 +4046,9 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="54"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C73" s="32">
         <v>84</v>
@@ -4069,28 +4057,28 @@
         <v>31</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="54"/>
+      <c r="H73" s="52"/>
       <c r="I73" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J73" s="32" t="s">
-        <v>7</v>
+      <c r="J73" s="32">
+        <v>82</v>
       </c>
       <c r="K73" s="2">
         <v>3</v>
       </c>
       <c r="L73" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A74" s="54"/>
+      <c r="A74" s="52"/>
       <c r="B74" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C74" s="16">
         <v>53</v>
@@ -4103,9 +4091,9 @@
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="54"/>
+      <c r="H74" s="52"/>
       <c r="I74" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J74" s="16">
         <v>29</v>
@@ -4114,28 +4102,28 @@
         <v>93</v>
       </c>
       <c r="L74" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A75" s="54"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C75" s="20" t="s">
-        <v>6</v>
+      <c r="C75" s="20">
+        <v>80</v>
       </c>
       <c r="D75" s="25">
         <v>8</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="54"/>
+      <c r="H75" s="52"/>
       <c r="I75" s="19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J75" s="20">
         <v>94</v>
@@ -4144,7 +4132,7 @@
         <v>18</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.15">
@@ -4176,51 +4164,51 @@
       <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
-      <c r="L78" s="48"/>
+      <c r="A78" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
     </row>
     <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
+      <c r="A79" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="46"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="46"/>
       <c r="F79" s="2"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="47"/>
-      <c r="J79" s="47"/>
-      <c r="K79" s="47"/>
-      <c r="L79" s="47"/>
+      <c r="H79" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
     </row>
     <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>0</v>
@@ -4228,16 +4216,16 @@
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
       <c r="H80" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>0</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K80" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>0</v>
@@ -4245,10 +4233,10 @@
     </row>
     <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A81" s="57" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C81" s="16">
         <v>59</v>
@@ -4257,15 +4245,15 @@
         <v>92</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="55" t="s">
-        <v>30</v>
+      <c r="H81" s="53" t="s">
+        <v>26</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J81" s="16">
         <v>3</v>
@@ -4274,7 +4262,7 @@
         <v>15</v>
       </c>
       <c r="L81" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
@@ -4293,9 +4281,9 @@
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="55"/>
+      <c r="H82" s="53"/>
       <c r="I82" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J82" s="32">
         <v>35</v>
@@ -4304,13 +4292,13 @@
         <v>94</v>
       </c>
       <c r="L82" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A83" s="57"/>
       <c r="B83" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C83" s="28">
         <v>10</v>
@@ -4319,13 +4307,13 @@
         <v>23</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="55"/>
+      <c r="H83" s="53"/>
       <c r="I83" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J83" s="28">
         <v>51</v>
@@ -4334,13 +4322,13 @@
         <v>93</v>
       </c>
       <c r="L83" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
       <c r="A84" s="57"/>
       <c r="B84" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C84" s="32">
         <v>29</v>
@@ -4349,16 +4337,16 @@
         <v>6</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="55"/>
+      <c r="H84" s="53"/>
       <c r="I84" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J84" s="32" t="s">
-        <v>6</v>
+      <c r="J84" s="32">
+        <v>80</v>
       </c>
       <c r="K84" s="2">
         <v>62</v>
@@ -4370,7 +4358,7 @@
     <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A85" s="58"/>
       <c r="B85" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="27">
         <v>55</v>
@@ -4379,13 +4367,13 @@
         <v>86</v>
       </c>
       <c r="E85" s="36" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="56"/>
+      <c r="H85" s="54"/>
       <c r="I85" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J85" s="29">
         <v>1</v>
@@ -4394,18 +4382,18 @@
         <v>17</v>
       </c>
       <c r="L85" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="51" t="s">
-        <v>29</v>
+      <c r="A86" s="55" t="s">
+        <v>25</v>
       </c>
       <c r="B86" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="33" t="s">
-        <v>4</v>
+      <c r="C86" s="33">
+        <v>75</v>
       </c>
       <c r="D86" s="37">
         <v>68</v>
@@ -4415,11 +4403,11 @@
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="53" t="s">
-        <v>29</v>
+      <c r="H86" s="51" t="s">
+        <v>25</v>
       </c>
       <c r="I86" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J86" s="32">
         <v>32</v>
@@ -4432,9 +4420,9 @@
       </c>
     </row>
     <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="52"/>
+      <c r="A87" s="56"/>
       <c r="B87" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C87" s="16">
         <v>11</v>
@@ -4443,13 +4431,13 @@
         <v>22</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="54"/>
+      <c r="H87" s="52"/>
       <c r="I87" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J87" s="16">
         <v>57</v>
@@ -4458,13 +4446,13 @@
         <v>83</v>
       </c>
       <c r="L87" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="52"/>
+      <c r="A88" s="56"/>
       <c r="B88" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C88" s="32">
         <v>31</v>
@@ -4473,16 +4461,16 @@
         <v>18</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="54"/>
+      <c r="H88" s="52"/>
       <c r="I88" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="J88" s="32" t="s">
-        <v>5</v>
+      <c r="J88" s="32">
+        <v>77</v>
       </c>
       <c r="K88" s="2">
         <v>71</v>
@@ -4492,9 +4480,9 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A89" s="52"/>
+      <c r="A89" s="56"/>
       <c r="B89" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C89" s="16">
         <v>53</v>
@@ -4503,13 +4491,13 @@
         <v>84</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="54"/>
+      <c r="H89" s="52"/>
       <c r="I89" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J89" s="16">
         <v>8</v>
@@ -4518,16 +4506,16 @@
         <v>36</v>
       </c>
       <c r="L89" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A90" s="52"/>
+      <c r="A90" s="56"/>
       <c r="B90" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C90" s="20" t="s">
-        <v>7</v>
+      <c r="C90" s="20">
+        <v>82</v>
       </c>
       <c r="D90" s="25">
         <v>66</v>
@@ -4537,9 +4525,9 @@
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="54"/>
+      <c r="H90" s="52"/>
       <c r="I90" s="19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J90" s="20">
         <v>26</v>
@@ -4548,11 +4536,39 @@
         <v>20</v>
       </c>
       <c r="L90" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="H86:H90"/>
+    <mergeCell ref="A63:L63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="H64:L64"/>
+    <mergeCell ref="A66:A70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="A71:A75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="A78:L78"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="H79:L79"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="H81:H85"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="H36:H40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="H41:H45"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="H49:L49"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="H51:H55"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="H26:H30"/>
     <mergeCell ref="A3:L3"/>
@@ -4567,34 +4583,6 @@
     <mergeCell ref="H19:L19"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="H21:H25"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="H79:L79"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="H81:H85"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B6:C15 B21:C30 B36:C45 B51:C60 B66:C75 B81:C90">
@@ -4868,33 +4856,33 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="44"/>
-      <c r="B1" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="B1" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
-      <c r="B2" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
+      <c r="B2" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="G2" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
@@ -4902,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>0</v>
@@ -4915,34 +4903,34 @@
         <v>0</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="49" t="s">
-        <v>24</v>
+      <c r="A4" s="47" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="16">
         <v>57</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>7</v>
+      <c r="D4" s="21">
+        <v>82</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H4" s="16">
         <v>10</v>
@@ -4955,9 +4943,9 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="49"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="16">
         <v>6</v>
@@ -4966,11 +4954,11 @@
         <v>32</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H5" s="16">
         <v>15</v>
@@ -4979,13 +4967,13 @@
         <v>84</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="49"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="16">
         <v>18</v>
@@ -4994,39 +4982,39 @@
         <v>93</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H6" s="16">
         <v>51</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>6</v>
+      <c r="I6" s="21">
+        <v>80</v>
       </c>
       <c r="J6" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="49"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" s="16">
         <v>59</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>3</v>
+      <c r="D7" s="21">
+        <v>74</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H7" s="16">
         <v>11</v>
@@ -5035,13 +5023,13 @@
         <v>35</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" s="18">
         <v>8</v>
@@ -5054,7 +5042,7 @@
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H8" s="29">
         <v>23</v>
@@ -5067,11 +5055,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="45" t="s">
-        <v>25</v>
+      <c r="A9" s="50" t="s">
+        <v>21</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" s="20">
         <v>22</v>
@@ -5080,11 +5068,11 @@
         <v>92</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H9" s="20">
         <v>1</v>
@@ -5093,26 +5081,26 @@
         <v>29</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="46"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C10" s="16">
         <v>53</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>5</v>
+      <c r="D10" s="21">
+        <v>77</v>
       </c>
       <c r="E10" s="22" t="s">
         <v>2</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H10" s="16">
         <v>17</v>
@@ -5121,13 +5109,13 @@
         <v>86</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="46"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" s="16">
         <v>3</v>
@@ -5136,11 +5124,11 @@
         <v>31</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H11" s="16">
         <v>26</v>
@@ -5149,13 +5137,13 @@
         <v>83</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="46"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" s="16">
         <v>20</v>
@@ -5168,7 +5156,7 @@
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H12" s="16">
         <v>94</v>
@@ -5181,15 +5169,15 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="46"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" s="16">
         <v>55</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>4</v>
+      <c r="D13" s="21">
+        <v>75</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>2</v>
@@ -5205,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="J13" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -5222,33 +5210,33 @@
     </row>
     <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" s="44"/>
-      <c r="B15" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
+      <c r="B15" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
-      <c r="B16" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
+      <c r="B16" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
+      <c r="G16" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="42"/>
@@ -5256,10 +5244,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>0</v>
@@ -5269,21 +5257,21 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="49" t="s">
-        <v>26</v>
+      <c r="A18" s="47" t="s">
+        <v>22</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C18" s="27">
         <v>59</v>
@@ -5292,11 +5280,11 @@
         <v>8</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="14" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H18" s="16">
         <v>83</v>
@@ -5305,26 +5293,26 @@
         <v>23</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="49"/>
+      <c r="A19" s="47"/>
       <c r="B19" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>4</v>
+      <c r="C19" s="16">
+        <v>75</v>
       </c>
       <c r="D19" s="21">
         <v>29</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H19" s="16">
         <v>55</v>
@@ -5333,13 +5321,13 @@
         <v>6</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="49"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C20" s="28">
         <v>22</v>
@@ -5354,20 +5342,20 @@
       <c r="G20" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>3</v>
+      <c r="H20" s="16">
+        <v>74</v>
       </c>
       <c r="I20" s="21">
         <v>26</v>
       </c>
       <c r="J20" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="49"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="21" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="16">
         <v>93</v>
@@ -5376,11 +5364,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H21" s="16">
         <v>17</v>
@@ -5393,9 +5381,9 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C22" s="29">
         <v>57</v>
@@ -5404,11 +5392,11 @@
         <v>1</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="17" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H22" s="29">
         <v>84</v>
@@ -5421,24 +5409,24 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="45" t="s">
-        <v>27</v>
+      <c r="A23" s="50" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>7</v>
+      <c r="C23" s="20">
+        <v>82</v>
       </c>
       <c r="D23" s="25">
         <v>32</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H23" s="20">
         <v>51</v>
@@ -5447,13 +5435,13 @@
         <v>11</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="46"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C24" s="16">
         <v>18</v>
@@ -5468,20 +5456,20 @@
       <c r="G24" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H24" s="16" t="s">
-        <v>6</v>
+      <c r="H24" s="16">
+        <v>80</v>
       </c>
       <c r="I24" s="21">
         <v>31</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="46"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="21" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" s="16">
         <v>86</v>
@@ -5490,11 +5478,11 @@
         <v>36</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H25" s="16">
         <v>15</v>
@@ -5507,9 +5495,9 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="46"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C26" s="16">
         <v>53</v>
@@ -5518,11 +5506,11 @@
         <v>10</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H26" s="16">
         <v>20</v>
@@ -5531,22 +5519,22 @@
         <v>94</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="46"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>5</v>
+      <c r="C27" s="16">
+        <v>77</v>
       </c>
       <c r="D27" s="21">
         <v>35</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="14" t="s">
@@ -5559,7 +5547,7 @@
         <v>92</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -5576,33 +5564,33 @@
     </row>
     <row r="29" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
+      <c r="B29" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
-      <c r="B30" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
+      <c r="B30" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
+      <c r="G30" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="42"/>
@@ -5610,10 +5598,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>0</v>
@@ -5623,21 +5611,21 @@
         <v>0</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="49" t="s">
-        <v>31</v>
+      <c r="A32" s="47" t="s">
+        <v>27</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C32" s="27">
         <v>59</v>
@@ -5646,11 +5634,11 @@
         <v>29</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H32" s="16">
         <v>8</v>
@@ -5659,22 +5647,22 @@
         <v>92</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="49"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>5</v>
+      <c r="C33" s="16">
+        <v>77</v>
       </c>
       <c r="D33" s="21">
         <v>23</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="30" t="s">
@@ -5687,13 +5675,13 @@
         <v>17</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="49"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C34" s="31">
         <v>1</v>
@@ -5702,11 +5690,11 @@
         <v>84</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H34" s="28">
         <v>53</v>
@@ -5715,11 +5703,11 @@
         <v>35</v>
       </c>
       <c r="J34" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="49"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="14" t="s">
         <v>1</v>
       </c>
@@ -5730,26 +5718,26 @@
         <v>11</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H35" s="32" t="s">
-        <v>4</v>
+      <c r="H35" s="32">
+        <v>75</v>
       </c>
       <c r="I35" s="2">
         <v>22</v>
       </c>
       <c r="J35" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="49"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C36" s="29">
         <v>51</v>
@@ -5758,11 +5746,11 @@
         <v>36</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H36" s="29">
         <v>6</v>
@@ -5771,24 +5759,24 @@
         <v>86</v>
       </c>
       <c r="J36" s="24" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="45" t="s">
-        <v>32</v>
+      <c r="A37" s="50" t="s">
+        <v>28</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>6</v>
+      <c r="C37" s="20">
+        <v>80</v>
       </c>
       <c r="D37" s="25">
         <v>15</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="19" t="s">
@@ -5801,13 +5789,13 @@
         <v>93</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="46"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C38" s="32">
         <v>10</v>
@@ -5816,11 +5804,11 @@
         <v>94</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H38" s="32">
         <v>57</v>
@@ -5829,11 +5817,11 @@
         <v>31</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="46"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
@@ -5844,26 +5832,26 @@
         <v>26</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H39" s="16" t="s">
-        <v>7</v>
+      <c r="H39" s="16">
+        <v>82</v>
       </c>
       <c r="I39" s="21">
         <v>18</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="46"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C40" s="32">
         <v>55</v>
@@ -5872,11 +5860,11 @@
         <v>32</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H40" s="16">
         <v>3</v>
@@ -5889,22 +5877,22 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="46"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="16" t="s">
-        <v>3</v>
+      <c r="C41" s="16">
+        <v>74</v>
       </c>
       <c r="D41" s="21">
         <v>20</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H41" s="20">
         <v>83</v>
@@ -5930,33 +5918,33 @@
     </row>
     <row r="43" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A43" s="44"/>
-      <c r="B43" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
+      <c r="B43" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
-      <c r="B44" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
+      <c r="B44" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="47"/>
+      <c r="G44" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
@@ -5964,10 +5952,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>0</v>
@@ -5977,21 +5965,21 @@
         <v>0</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="49" t="s">
-        <v>33</v>
+      <c r="A46" s="47" t="s">
+        <v>29</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C46" s="16">
         <v>53</v>
@@ -6000,11 +5988,11 @@
         <v>20</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H46" s="16">
         <v>3</v>
@@ -6013,26 +6001,26 @@
         <v>36</v>
       </c>
       <c r="J46" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="49"/>
+      <c r="A47" s="47"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="32" t="s">
-        <v>3</v>
+      <c r="C47" s="32">
+        <v>74</v>
       </c>
       <c r="D47" s="2">
         <v>94</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H47" s="32">
         <v>84</v>
@@ -6045,9 +6033,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="49"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C48" s="28">
         <v>11</v>
@@ -6060,7 +6048,7 @@
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H48" s="28">
         <v>51</v>
@@ -6069,13 +6057,13 @@
         <v>15</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="49"/>
+      <c r="A49" s="47"/>
       <c r="B49" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C49" s="32">
         <v>26</v>
@@ -6084,26 +6072,26 @@
         <v>8</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="32" t="s">
-        <v>6</v>
+      <c r="H49" s="32">
+        <v>80</v>
       </c>
       <c r="I49" s="2">
         <v>86</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
+      <c r="A50" s="48"/>
       <c r="B50" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C50" s="29">
         <v>55</v>
@@ -6112,11 +6100,11 @@
         <v>17</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H50" s="29">
         <v>6</v>
@@ -6129,24 +6117,24 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="46" t="s">
-        <v>34</v>
+      <c r="A51" s="49" t="s">
+        <v>30</v>
       </c>
       <c r="B51" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="32" t="s">
-        <v>5</v>
+      <c r="C51" s="32">
+        <v>77</v>
       </c>
       <c r="D51" s="2">
         <v>92</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H51" s="32">
         <v>31</v>
@@ -6159,9 +6147,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="46"/>
+      <c r="A52" s="49"/>
       <c r="B52" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C52" s="16">
         <v>1</v>
@@ -6174,7 +6162,7 @@
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H52" s="16">
         <v>57</v>
@@ -6183,13 +6171,13 @@
         <v>23</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="46"/>
+      <c r="A53" s="49"/>
       <c r="B53" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C53" s="32">
         <v>29</v>
@@ -6198,26 +6186,26 @@
         <v>22</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H53" s="32" t="s">
-        <v>7</v>
+      <c r="H53" s="32">
+        <v>82</v>
       </c>
       <c r="I53" s="2">
         <v>93</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="46"/>
+      <c r="A54" s="49"/>
       <c r="B54" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C54" s="16">
         <v>59</v>
@@ -6226,11 +6214,11 @@
         <v>18</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H54" s="16">
         <v>10</v>
@@ -6239,26 +6227,26 @@
         <v>32</v>
       </c>
       <c r="J54" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="46"/>
+      <c r="A55" s="49"/>
       <c r="B55" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="20" t="s">
-        <v>4</v>
+      <c r="C55" s="20">
+        <v>75</v>
       </c>
       <c r="D55" s="25">
         <v>83</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H55" s="20">
         <v>35</v>
@@ -6284,33 +6272,33 @@
     </row>
     <row r="57" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A57" s="44"/>
-      <c r="B57" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
+      <c r="B57" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="45"/>
+      <c r="D57" s="45"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="45"/>
+      <c r="J57" s="45"/>
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
-      <c r="B58" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="47"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="47"/>
+      <c r="B58" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H58" s="47"/>
-      <c r="I58" s="47"/>
-      <c r="J58" s="47"/>
+      <c r="G58" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="46"/>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="42"/>
@@ -6318,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>0</v>
@@ -6331,21 +6319,21 @@
         <v>0</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="49" t="s">
-        <v>28</v>
+      <c r="A60" s="47" t="s">
+        <v>24</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C60" s="16">
         <v>59</v>
@@ -6358,7 +6346,7 @@
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H60" s="16">
         <v>35</v>
@@ -6367,26 +6355,26 @@
         <v>23</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="49"/>
+      <c r="A61" s="47"/>
       <c r="B61" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="32" t="s">
-        <v>3</v>
+      <c r="C61" s="32">
+        <v>74</v>
       </c>
       <c r="D61" s="2">
         <v>6</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H61" s="32">
         <v>83</v>
@@ -6395,13 +6383,13 @@
         <v>20</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A62" s="49"/>
+      <c r="A62" s="47"/>
       <c r="B62" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C62" s="28">
         <v>26</v>
@@ -6410,11 +6398,11 @@
         <v>17</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H62" s="28">
         <v>57</v>
@@ -6427,9 +6415,9 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="49"/>
+      <c r="A63" s="47"/>
       <c r="B63" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C63" s="32">
         <v>92</v>
@@ -6438,26 +6426,26 @@
         <v>10</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H63" s="32" t="s">
+      <c r="H63" s="32">
+        <v>77</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="I63" s="2">
-        <v>1</v>
-      </c>
-      <c r="J63" s="34" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="49"/>
+      <c r="A64" s="47"/>
       <c r="B64" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C64" s="29">
         <v>55</v>
@@ -6470,7 +6458,7 @@
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H64" s="29">
         <v>36</v>
@@ -6479,28 +6467,28 @@
         <v>15</v>
       </c>
       <c r="J64" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="45" t="s">
-        <v>35</v>
+      <c r="A65" s="50" t="s">
+        <v>31</v>
       </c>
       <c r="B65" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="32" t="s">
-        <v>4</v>
+      <c r="C65" s="32">
+        <v>75</v>
       </c>
       <c r="D65" s="2">
         <v>11</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H65" s="32">
         <v>86</v>
@@ -6513,9 +6501,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="46"/>
+      <c r="A66" s="49"/>
       <c r="B66" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C66" s="16">
         <v>32</v>
@@ -6524,11 +6512,11 @@
         <v>22</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H66" s="16">
         <v>51</v>
@@ -6541,9 +6529,9 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="46"/>
+      <c r="A67" s="49"/>
       <c r="B67" s="30" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C67" s="32">
         <v>84</v>
@@ -6552,26 +6540,26 @@
         <v>31</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H67" s="32" t="s">
-        <v>7</v>
+      <c r="H67" s="32">
+        <v>82</v>
       </c>
       <c r="I67" s="2">
         <v>3</v>
       </c>
       <c r="J67" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="46"/>
+      <c r="A68" s="49"/>
       <c r="B68" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C68" s="16">
         <v>53</v>
@@ -6584,7 +6572,7 @@
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H68" s="16">
         <v>29</v>
@@ -6593,26 +6581,26 @@
         <v>93</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="46"/>
+      <c r="A69" s="49"/>
       <c r="B69" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="20" t="s">
-        <v>6</v>
+      <c r="C69" s="20">
+        <v>80</v>
       </c>
       <c r="D69" s="25">
         <v>8</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H69" s="20">
         <v>94</v>
@@ -6621,7 +6609,7 @@
         <v>18</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="10" customHeight="1" x14ac:dyDescent="0.2">
@@ -6638,33 +6626,33 @@
     </row>
     <row r="71" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A71" s="44"/>
-      <c r="B71" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
+      <c r="B71" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
-      <c r="B72" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="47"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="47"/>
+      <c r="B72" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="H72" s="47"/>
-      <c r="I72" s="47"/>
-      <c r="J72" s="47"/>
+      <c r="G72" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="46"/>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="42"/>
@@ -6672,10 +6660,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>0</v>
@@ -6685,21 +6673,21 @@
         <v>0</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="49" t="s">
-        <v>30</v>
+      <c r="A74" s="47" t="s">
+        <v>26</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C74" s="16">
         <v>59</v>
@@ -6708,11 +6696,11 @@
         <v>92</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H74" s="16">
         <v>3</v>
@@ -6721,16 +6709,16 @@
         <v>15</v>
       </c>
       <c r="J74" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="49"/>
+      <c r="A75" s="47"/>
       <c r="B75" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C75" s="32" t="s">
-        <v>3</v>
+      <c r="C75" s="32">
+        <v>74</v>
       </c>
       <c r="D75" s="2">
         <v>69</v>
@@ -6740,7 +6728,7 @@
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H75" s="32">
         <v>35</v>
@@ -6749,13 +6737,13 @@
         <v>94</v>
       </c>
       <c r="J75" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
+      <c r="A76" s="47"/>
       <c r="B76" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C76" s="28">
         <v>10</v>
@@ -6764,11 +6752,11 @@
         <v>23</v>
       </c>
       <c r="E76" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H76" s="28">
         <v>51</v>
@@ -6777,13 +6765,13 @@
         <v>93</v>
       </c>
       <c r="J76" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="49"/>
+      <c r="A77" s="47"/>
       <c r="B77" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C77" s="32">
         <v>29</v>
@@ -6792,14 +6780,14 @@
         <v>6</v>
       </c>
       <c r="E77" s="34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H77" s="32" t="s">
-        <v>6</v>
+      <c r="H77" s="32">
+        <v>80</v>
       </c>
       <c r="I77" s="2">
         <v>62</v>
@@ -6809,9 +6797,9 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="50"/>
+      <c r="A78" s="48"/>
       <c r="B78" s="17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C78" s="27">
         <v>55</v>
@@ -6820,11 +6808,11 @@
         <v>86</v>
       </c>
       <c r="E78" s="36" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H78" s="29">
         <v>1</v>
@@ -6833,18 +6821,18 @@
         <v>17</v>
       </c>
       <c r="J78" s="24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="46" t="s">
-        <v>29</v>
+      <c r="A79" s="49" t="s">
+        <v>25</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="33" t="s">
-        <v>4</v>
+      <c r="C79" s="33">
+        <v>75</v>
       </c>
       <c r="D79" s="37">
         <v>68</v>
@@ -6854,7 +6842,7 @@
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H79" s="32">
         <v>32</v>
@@ -6867,9 +6855,9 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="46"/>
+      <c r="A80" s="49"/>
       <c r="B80" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C80" s="16">
         <v>11</v>
@@ -6878,11 +6866,11 @@
         <v>22</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H80" s="16">
         <v>57</v>
@@ -6891,13 +6879,13 @@
         <v>83</v>
       </c>
       <c r="J80" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="46"/>
+      <c r="A81" s="49"/>
       <c r="B81" s="30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C81" s="32">
         <v>31</v>
@@ -6906,14 +6894,14 @@
         <v>18</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H81" s="32" t="s">
-        <v>5</v>
+      <c r="H81" s="32">
+        <v>77</v>
       </c>
       <c r="I81" s="2">
         <v>71</v>
@@ -6923,9 +6911,9 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="46"/>
+      <c r="A82" s="49"/>
       <c r="B82" s="14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C82" s="16">
         <v>53</v>
@@ -6934,11 +6922,11 @@
         <v>84</v>
       </c>
       <c r="E82" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H82" s="16">
         <v>8</v>
@@ -6947,16 +6935,16 @@
         <v>36</v>
       </c>
       <c r="J82" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="46"/>
+      <c r="A83" s="49"/>
       <c r="B83" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="20" t="s">
-        <v>7</v>
+      <c r="C83" s="20">
+        <v>82</v>
       </c>
       <c r="D83" s="25">
         <v>66</v>
@@ -6966,7 +6954,7 @@
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H83" s="20">
         <v>26</v>
@@ -6975,21 +6963,19 @@
         <v>20</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="A74:A78"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="G58:J58"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="A65:A69"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B71:J71"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A4:A8"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="G30:J30"/>
@@ -7002,14 +6988,16 @@
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="A46:A50"/>
     <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B71:J71"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C14 B18:C28 B32:C42 B46:C56 B60:C70 B74:C83">
     <cfRule type="expression" dxfId="27" priority="50">
@@ -7108,29 +7096,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f8e6109263404e4da1831cd151bd9fd5>
-    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </kd8ebdb17ae1461db4d8c38e130fcffb>
-    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -7377,41 +7351,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f8e6109263404e4da1831cd151bd9fd5>
+    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </kd8ebdb17ae1461db4d8c38e130fcffb>
+    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7430,10 +7401,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MIO_Spielplan.xlsx
+++ b/MIO_Spielplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A2C549-82E9-B446-A0AD-BED539AAFACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056D3FE1-C1D4-FD46-A863-0578AF48B38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="17" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="33">
   <si>
     <t>Klasse</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>15:25-15:35</t>
+  </si>
+  <si>
+    <t>Move-it-Over</t>
   </si>
 </sst>
 </file>
@@ -700,25 +703,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -737,6 +728,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1163,15 +1166,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$B$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$B$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$C$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$C$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$D$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$D$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1179,15 +1182,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$I$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$I$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$J$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$J$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$K$1" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" fmlaLink="$K$1" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2107,7 +2110,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990AFEB4-A92B-1849-96F5-AAADB6DDF155}">
-  <dimension ref="A1:N90"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.83203125" style="1" customWidth="1"/>
@@ -2118,13 +2124,13 @@
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="40" t="b">
         <v>1</v>
@@ -2132,19 +2138,19 @@
       <c r="F1" s="40"/>
       <c r="H1" s="40"/>
       <c r="I1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1" s="40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1" s="40"/>
     </row>
     <row r="3" spans="1:14" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
@@ -2158,2526 +2164,2544 @@
       <c r="K3" s="45"/>
       <c r="L3" s="45"/>
     </row>
-    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="46" t="s">
+    <row r="5" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+    </row>
+    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A6" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="46" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+    </row>
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.15">
+      <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="8" t="s">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N5" s="40"/>
-    </row>
-    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="53" t="s">
+      <c r="N7" s="40"/>
+    </row>
+    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A8" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C8" s="16">
         <v>57</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D8" s="21">
         <v>82</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>2</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="16">
-        <v>10</v>
-      </c>
-      <c r="K6" s="21">
-        <v>63</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="53"/>
-      <c r="B7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="16">
-        <v>6</v>
-      </c>
-      <c r="D7" s="21">
-        <v>32</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="16">
-        <v>15</v>
-      </c>
-      <c r="K7" s="21">
-        <v>84</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A8" s="53"/>
-      <c r="B8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="16">
-        <v>18</v>
-      </c>
-      <c r="D8" s="21">
-        <v>93</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>4</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="49" t="s">
+        <v>20</v>
+      </c>
       <c r="I8" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J8" s="16">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="K8" s="21">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A9" s="53"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="16">
-        <v>59</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D9" s="21">
+        <v>32</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="49"/>
       <c r="I9" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="16">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K9" s="21">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="L9" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="54"/>
-      <c r="B10" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="18">
-        <v>8</v>
-      </c>
-      <c r="D10" s="23">
-        <v>62</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A10" s="49"/>
+      <c r="B10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="16">
+        <v>18</v>
+      </c>
+      <c r="D10" s="21">
+        <v>93</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="29">
-        <v>23</v>
-      </c>
-      <c r="K10" s="23">
-        <v>71</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="20">
-        <v>22</v>
-      </c>
-      <c r="D11" s="25">
-        <v>92</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>4</v>
+      <c r="H10" s="49"/>
+      <c r="I10" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="16">
+        <v>51</v>
+      </c>
+      <c r="K10" s="21">
+        <v>80</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A11" s="49"/>
+      <c r="B11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="16">
+        <v>59</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>2</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="19" t="s">
+      <c r="H11" s="49"/>
+      <c r="I11" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="J11" s="20">
-        <v>1</v>
-      </c>
-      <c r="K11" s="25">
-        <v>29</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A12" s="52"/>
-      <c r="B12" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16">
-        <v>53</v>
-      </c>
-      <c r="D12" s="21">
-        <v>77</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>2</v>
+      <c r="J11" s="16">
+        <v>11</v>
+      </c>
+      <c r="K11" s="21">
+        <v>35</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="50"/>
+      <c r="B12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="18">
+        <v>8</v>
+      </c>
+      <c r="D12" s="23">
+        <v>62</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="16">
-        <v>17</v>
-      </c>
-      <c r="K12" s="21">
-        <v>86</v>
-      </c>
-      <c r="L12" s="22" t="s">
+      <c r="H12" s="50"/>
+      <c r="I12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="29">
+        <v>23</v>
+      </c>
+      <c r="K12" s="23">
+        <v>71</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="20">
+        <v>22</v>
+      </c>
+      <c r="D13" s="25">
+        <v>92</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="52"/>
-      <c r="B13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="16">
-        <v>3</v>
-      </c>
-      <c r="D13" s="21">
-        <v>31</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>8</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="16">
-        <v>26</v>
-      </c>
-      <c r="K13" s="21">
-        <v>83</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>4</v>
+      <c r="H13" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="20">
+        <v>1</v>
+      </c>
+      <c r="K13" s="25">
+        <v>29</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A14" s="52"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="16">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D14" s="21">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="52"/>
+      <c r="H14" s="47"/>
       <c r="I14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="16">
+        <v>17</v>
+      </c>
+      <c r="K14" s="21">
+        <v>86</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="16">
-        <v>94</v>
-      </c>
-      <c r="K14" s="21">
-        <v>66</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.15">
-      <c r="A15" s="52"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="16">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="D15" s="21">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="52"/>
+      <c r="H15" s="47"/>
       <c r="I15" s="14" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J15" s="16">
+        <v>26</v>
+      </c>
+      <c r="K15" s="21">
+        <v>83</v>
+      </c>
+      <c r="L15" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20" x14ac:dyDescent="0.15">
+      <c r="A16" s="47"/>
+      <c r="B16" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="16">
+        <v>20</v>
+      </c>
+      <c r="D16" s="21">
+        <v>69</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="16">
+        <v>94</v>
+      </c>
+      <c r="K16" s="21">
+        <v>66</v>
+      </c>
+      <c r="L16" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A17" s="47"/>
+      <c r="B17" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="16">
+        <v>55</v>
+      </c>
+      <c r="D17" s="21">
+        <v>75</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="16">
         <v>68</v>
       </c>
-      <c r="K15" s="21">
+      <c r="K17" s="21">
         <v>36</v>
       </c>
-      <c r="L15" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+      <c r="L17" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-    </row>
-    <row r="19" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A19" s="46" t="s">
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+    </row>
+    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A21" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="46" t="s">
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-    </row>
-    <row r="20" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+    </row>
+    <row r="22" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D22" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="8" t="s">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J22" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K22" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A21" s="53" t="s">
+    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A23" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B23" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C23" s="27">
         <v>59</v>
       </c>
-      <c r="D21" s="21">
-        <v>8</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D23" s="21">
+        <v>8</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="16">
-        <v>83</v>
-      </c>
-      <c r="K21" s="39">
-        <v>23</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="53"/>
-      <c r="B22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="16">
-        <v>75</v>
-      </c>
-      <c r="D22" s="21">
-        <v>29</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J22" s="16">
-        <v>55</v>
-      </c>
-      <c r="K22" s="21">
-        <v>6</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A23" s="53"/>
-      <c r="B23" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="28">
-        <v>22</v>
-      </c>
-      <c r="D23" s="21">
-        <v>68</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="53"/>
+      <c r="H23" s="49" t="s">
+        <v>22</v>
+      </c>
       <c r="I23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="16">
+        <v>83</v>
+      </c>
+      <c r="K23" s="39">
+        <v>23</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A24" s="49"/>
+      <c r="B24" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J23" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="21">
-        <v>26</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A24" s="53"/>
-      <c r="B24" s="14" t="s">
-        <v>4</v>
-      </c>
       <c r="C24" s="16">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D24" s="21">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="49"/>
       <c r="I24" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" s="16">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="K24" s="21">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="L24" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
-      <c r="B25" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="29">
-        <v>57</v>
-      </c>
-      <c r="D25" s="23">
-        <v>1</v>
-      </c>
-      <c r="E25" s="24" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A25" s="49"/>
+      <c r="B25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="28">
+        <v>22</v>
+      </c>
+      <c r="D25" s="21">
+        <v>68</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>1</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="17" t="s">
+      <c r="H25" s="49"/>
+      <c r="I25" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="21">
+        <v>26</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A26" s="49"/>
+      <c r="B26" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J25" s="29">
-        <v>84</v>
-      </c>
-      <c r="K25" s="23">
-        <v>69</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="20">
-        <v>82</v>
-      </c>
-      <c r="D26" s="25">
-        <v>32</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>8</v>
+      <c r="C26" s="16">
+        <v>93</v>
+      </c>
+      <c r="D26" s="21">
+        <v>3</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="19" t="s">
+      <c r="H26" s="49"/>
+      <c r="I26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="16">
+        <v>17</v>
+      </c>
+      <c r="K26" s="21">
+        <v>62</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="50"/>
+      <c r="B27" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J26" s="20">
-        <v>51</v>
-      </c>
-      <c r="K26" s="25">
-        <v>11</v>
-      </c>
-      <c r="L26" s="26" t="s">
+      <c r="C27" s="29">
+        <v>57</v>
+      </c>
+      <c r="D27" s="23">
+        <v>1</v>
+      </c>
+      <c r="E27" s="24" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A27" s="52"/>
-      <c r="B27" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="16">
-        <v>18</v>
-      </c>
-      <c r="D27" s="21">
-        <v>63</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="14" t="s">
+      <c r="H27" s="50"/>
+      <c r="I27" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="29">
+        <v>84</v>
+      </c>
+      <c r="K27" s="23">
+        <v>69</v>
+      </c>
+      <c r="L27" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J27" s="16">
-        <v>80</v>
-      </c>
-      <c r="K27" s="21">
-        <v>31</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="52"/>
-      <c r="B28" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="16">
-        <v>86</v>
-      </c>
-      <c r="D28" s="21">
-        <v>36</v>
-      </c>
-      <c r="E28" s="22" t="s">
+      <c r="C28" s="20">
+        <v>82</v>
+      </c>
+      <c r="D28" s="25">
+        <v>32</v>
+      </c>
+      <c r="E28" s="26" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J28" s="16">
-        <v>15</v>
-      </c>
-      <c r="K28" s="21">
-        <v>66</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>1</v>
+      <c r="H28" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J28" s="20">
+        <v>51</v>
+      </c>
+      <c r="K28" s="25">
+        <v>11</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A29" s="52"/>
+      <c r="A29" s="47"/>
       <c r="B29" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="16">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D29" s="21">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="52"/>
+      <c r="H29" s="47"/>
       <c r="I29" s="14" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J29" s="16">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="K29" s="21">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="L29" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A30" s="47"/>
+      <c r="B30" s="14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A30" s="52"/>
-      <c r="B30" s="14" t="s">
-        <v>2</v>
-      </c>
       <c r="C30" s="16">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D30" s="21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" s="22" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="52"/>
+      <c r="H30" s="47"/>
       <c r="I30" s="14" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J30" s="16">
+        <v>15</v>
+      </c>
+      <c r="K30" s="21">
+        <v>66</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A31" s="47"/>
+      <c r="B31" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="16">
+        <v>53</v>
+      </c>
+      <c r="D31" s="21">
+        <v>10</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="16">
+        <v>20</v>
+      </c>
+      <c r="K31" s="21">
+        <v>94</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A32" s="47"/>
+      <c r="B32" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="16">
+        <v>77</v>
+      </c>
+      <c r="D32" s="21">
+        <v>35</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="16">
         <v>71</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K32" s="21">
         <v>92</v>
       </c>
-      <c r="L30" s="22" t="s">
+      <c r="L32" s="22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-    </row>
-    <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="46" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+    </row>
+    <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A36" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="46" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-    </row>
-    <row r="35" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+    </row>
+    <row r="37" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D37" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="8" t="s">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J37" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K37" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="L37" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A36" s="53" t="s">
+    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A38" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B38" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C38" s="27">
         <v>59</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D38" s="35">
         <v>29</v>
       </c>
-      <c r="E36" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" s="16">
-        <v>8</v>
-      </c>
-      <c r="K36" s="21">
-        <v>92</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="53"/>
-      <c r="B37" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="16">
-        <v>77</v>
-      </c>
-      <c r="D37" s="21">
-        <v>23</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="32">
-        <v>63</v>
-      </c>
-      <c r="K37" s="2">
-        <v>17</v>
-      </c>
-      <c r="L37" s="34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A38" s="53"/>
-      <c r="B38" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="31">
-        <v>1</v>
-      </c>
-      <c r="D38" s="2">
-        <v>84</v>
-      </c>
-      <c r="E38" s="34" t="s">
-        <v>4</v>
+      <c r="E38" s="36" t="s">
+        <v>8</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="53"/>
+      <c r="H38" s="49" t="s">
+        <v>27</v>
+      </c>
       <c r="I38" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J38" s="28">
-        <v>53</v>
+        <v>5</v>
+      </c>
+      <c r="J38" s="16">
+        <v>8</v>
       </c>
       <c r="K38" s="21">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="L38" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A39" s="53"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="16">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D39" s="21">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="53"/>
+      <c r="H39" s="49"/>
       <c r="I39" s="30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" s="32">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="K39" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L39" s="34" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="54"/>
-      <c r="B40" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="29">
-        <v>51</v>
-      </c>
-      <c r="D40" s="23">
-        <v>36</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>8</v>
+    <row r="40" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A40" s="49"/>
+      <c r="B40" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="31">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>84</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>4</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="17" t="s">
+      <c r="H40" s="49"/>
+      <c r="I40" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J40" s="28">
+        <v>53</v>
+      </c>
+      <c r="K40" s="21">
+        <v>35</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A41" s="49"/>
+      <c r="B41" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
+        <v>69</v>
+      </c>
+      <c r="D41" s="21">
+        <v>11</v>
+      </c>
+      <c r="E41" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="J40" s="29">
-        <v>6</v>
-      </c>
-      <c r="K40" s="23">
-        <v>86</v>
-      </c>
-      <c r="L40" s="24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="20">
-        <v>80</v>
-      </c>
-      <c r="D41" s="25">
-        <v>15</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>6</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="20">
-        <v>68</v>
-      </c>
-      <c r="K41" s="25">
-        <v>93</v>
-      </c>
-      <c r="L41" s="26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="52"/>
-      <c r="B42" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="32">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2">
-        <v>94</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>4</v>
+      <c r="H41" s="49"/>
+      <c r="I41" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="32">
+        <v>75</v>
+      </c>
+      <c r="K41" s="2">
+        <v>22</v>
+      </c>
+      <c r="L41" s="34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="50"/>
+      <c r="B42" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="29">
+        <v>51</v>
+      </c>
+      <c r="D42" s="23">
+        <v>36</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>8</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="J42" s="32">
-        <v>57</v>
-      </c>
-      <c r="K42" s="2">
-        <v>31</v>
-      </c>
-      <c r="L42" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="52"/>
-      <c r="B43" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="16">
-        <v>71</v>
-      </c>
-      <c r="D43" s="21">
-        <v>26</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>8</v>
+      <c r="H42" s="50"/>
+      <c r="I42" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="29">
+        <v>6</v>
+      </c>
+      <c r="K42" s="23">
+        <v>86</v>
+      </c>
+      <c r="L42" s="24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="20">
+        <v>80</v>
+      </c>
+      <c r="D43" s="25">
+        <v>15</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="J43" s="16">
-        <v>82</v>
-      </c>
-      <c r="K43" s="21">
-        <v>18</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>6</v>
+      <c r="H43" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="20">
+        <v>68</v>
+      </c>
+      <c r="K43" s="25">
+        <v>93</v>
+      </c>
+      <c r="L43" s="26" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A44" s="52"/>
+      <c r="A44" s="47"/>
       <c r="B44" s="30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44" s="32">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="16">
-        <v>3</v>
-      </c>
-      <c r="K44" s="21">
-        <v>66</v>
-      </c>
-      <c r="L44" s="22" t="s">
-        <v>1</v>
+      <c r="H44" s="47"/>
+      <c r="I44" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="J44" s="32">
+        <v>57</v>
+      </c>
+      <c r="K44" s="2">
+        <v>31</v>
+      </c>
+      <c r="L44" s="34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A45" s="52"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="C45" s="16">
+        <v>71</v>
       </c>
       <c r="D45" s="21">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="19" t="s">
+      <c r="H45" s="47"/>
+      <c r="I45" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="16">
+        <v>82</v>
+      </c>
+      <c r="K45" s="21">
+        <v>18</v>
+      </c>
+      <c r="L45" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A46" s="47"/>
+      <c r="B46" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="32">
+        <v>55</v>
+      </c>
+      <c r="D46" s="2">
+        <v>32</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="16">
+        <v>3</v>
+      </c>
+      <c r="K46" s="21">
+        <v>66</v>
+      </c>
+      <c r="L46" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A47" s="47"/>
+      <c r="B47" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="21">
+        <v>20</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="20">
+      <c r="J47" s="20">
         <v>83</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K47" s="25">
         <v>62</v>
       </c>
-      <c r="L45" s="26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
+      <c r="L47" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+    </row>
+    <row r="50" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
-    </row>
-    <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="46" t="s">
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+    </row>
+    <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A51" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="46" t="s">
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="46"/>
-      <c r="L49" s="46"/>
-    </row>
-    <row r="50" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="8" t="s">
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48"/>
+    </row>
+    <row r="52" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C52" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D52" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="8" t="s">
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I52" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J52" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K52" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="L52" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A51" s="53" t="s">
+    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A53" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B53" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C53" s="16">
         <v>53</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D53" s="21">
         <v>20</v>
       </c>
-      <c r="E51" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="I51" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J51" s="16">
-        <v>3</v>
-      </c>
-      <c r="K51" s="21">
-        <v>36</v>
-      </c>
-      <c r="L51" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="53"/>
-      <c r="B52" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="2">
-        <v>94</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="53"/>
-      <c r="I52" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="32">
-        <v>84</v>
-      </c>
-      <c r="K52" s="2">
-        <v>63</v>
-      </c>
-      <c r="L52" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A53" s="53"/>
-      <c r="B53" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="28">
-        <v>11</v>
-      </c>
-      <c r="D53" s="21">
-        <v>68</v>
-      </c>
       <c r="E53" s="22" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="53"/>
+      <c r="H53" s="49" t="s">
+        <v>29</v>
+      </c>
       <c r="I53" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J53" s="28">
-        <v>51</v>
+        <v>5</v>
+      </c>
+      <c r="J53" s="16">
+        <v>3</v>
       </c>
       <c r="K53" s="21">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A54" s="53"/>
+      <c r="A54" s="49"/>
       <c r="B54" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="32">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>3</v>
       </c>
       <c r="D54" s="2">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="53"/>
+      <c r="H54" s="49"/>
       <c r="I54" s="30" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J54" s="32">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K54" s="2">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="54"/>
-      <c r="B55" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="29">
-        <v>55</v>
-      </c>
-      <c r="D55" s="23">
-        <v>17</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A55" s="49"/>
+      <c r="B55" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="28">
+        <v>11</v>
+      </c>
+      <c r="D55" s="21">
+        <v>68</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>1</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="17" t="s">
+      <c r="H55" s="49"/>
+      <c r="I55" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J55" s="28">
+        <v>51</v>
+      </c>
+      <c r="K55" s="21">
+        <v>15</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A56" s="49"/>
+      <c r="B56" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="32">
+        <v>26</v>
+      </c>
+      <c r="D56" s="2">
+        <v>8</v>
+      </c>
+      <c r="E56" s="34" t="s">
         <v>5</v>
-      </c>
-      <c r="J55" s="29">
-        <v>6</v>
-      </c>
-      <c r="K55" s="23">
-        <v>66</v>
-      </c>
-      <c r="L55" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="32">
-        <v>77</v>
-      </c>
-      <c r="D56" s="2">
-        <v>92</v>
-      </c>
-      <c r="E56" s="34" t="s">
-        <v>4</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="51" t="s">
-        <v>30</v>
-      </c>
+      <c r="H56" s="49"/>
       <c r="I56" s="30" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J56" s="32">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K56" s="2">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A57" s="52"/>
-      <c r="B57" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="16">
-        <v>1</v>
-      </c>
-      <c r="D57" s="21">
-        <v>71</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="50"/>
+      <c r="B57" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="29">
+        <v>55</v>
+      </c>
+      <c r="D57" s="23">
+        <v>17</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>6</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="52"/>
-      <c r="I57" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J57" s="16">
-        <v>57</v>
-      </c>
-      <c r="K57" s="21">
-        <v>23</v>
-      </c>
-      <c r="L57" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="52"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="29">
+        <v>6</v>
+      </c>
+      <c r="K57" s="23">
+        <v>66</v>
+      </c>
+      <c r="L57" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="46" t="s">
+        <v>30</v>
+      </c>
       <c r="B58" s="30" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C58" s="32">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="52"/>
+      <c r="H58" s="46" t="s">
+        <v>30</v>
+      </c>
       <c r="I58" s="30" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J58" s="32">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="K58" s="2">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A59" s="52"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C59" s="16">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D59" s="21">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="52"/>
+      <c r="H59" s="47"/>
       <c r="I59" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J59" s="16">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="K59" s="21">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L59" s="22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A60" s="52"/>
-      <c r="B60" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="20">
-        <v>75</v>
-      </c>
-      <c r="D60" s="25">
-        <v>83</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>4</v>
+      <c r="A60" s="47"/>
+      <c r="B60" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="32">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2">
+        <v>22</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>6</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="20">
+      <c r="H60" s="47"/>
+      <c r="I60" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J60" s="32">
+        <v>82</v>
+      </c>
+      <c r="K60" s="2">
+        <v>93</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A61" s="47"/>
+      <c r="B61" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="16">
+        <v>59</v>
+      </c>
+      <c r="D61" s="21">
+        <v>18</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J61" s="16">
+        <v>10</v>
+      </c>
+      <c r="K61" s="21">
+        <v>32</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A62" s="47"/>
+      <c r="B62" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="20">
+        <v>75</v>
+      </c>
+      <c r="D62" s="25">
+        <v>83</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="20">
         <v>35</v>
       </c>
-      <c r="K60" s="25">
+      <c r="K62" s="25">
         <v>69</v>
       </c>
-      <c r="L60" s="26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-    </row>
-    <row r="63" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A63" s="45" t="s">
+      <c r="L62" s="26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+    </row>
+    <row r="65" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A65" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
-      <c r="L63" s="45"/>
-    </row>
-    <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="46" t="s">
+      <c r="B65" s="45"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+    </row>
+    <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A66" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B64" s="46"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="46" t="s">
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="I64" s="46"/>
-      <c r="J64" s="46"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="46"/>
-    </row>
-    <row r="65" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="8" t="s">
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
+      <c r="L66" s="48"/>
+    </row>
+    <row r="67" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C67" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D67" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="8" t="s">
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I65" s="9" t="s">
+      <c r="I67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J67" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K67" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L65" s="9" t="s">
+      <c r="L67" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A66" s="53" t="s">
+    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A68" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B68" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C68" s="16">
         <v>59</v>
       </c>
-      <c r="D66" s="21">
+      <c r="D68" s="21">
         <v>63</v>
       </c>
-      <c r="E66" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="I66" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="16">
-        <v>35</v>
-      </c>
-      <c r="K66" s="21">
-        <v>23</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="53"/>
-      <c r="B67" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="2">
-        <v>6</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" s="4"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J67" s="32">
-        <v>83</v>
-      </c>
-      <c r="K67" s="2">
-        <v>20</v>
-      </c>
-      <c r="L67" s="34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A68" s="53"/>
-      <c r="B68" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C68" s="28">
-        <v>26</v>
-      </c>
-      <c r="D68" s="21">
-        <v>17</v>
-      </c>
       <c r="E68" s="22" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="53"/>
+      <c r="H68" s="49" t="s">
+        <v>24</v>
+      </c>
       <c r="I68" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J68" s="28">
-        <v>57</v>
+        <v>8</v>
+      </c>
+      <c r="J68" s="16">
+        <v>35</v>
       </c>
       <c r="K68" s="21">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="L68" s="22" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A69" s="53"/>
+      <c r="A69" s="49"/>
       <c r="B69" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C69" s="32">
-        <v>92</v>
+        <v>2</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>3</v>
       </c>
       <c r="D69" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E69" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="53"/>
+      <c r="H69" s="49"/>
       <c r="I69" s="30" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="32">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K69" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L69" s="34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="54"/>
-      <c r="B70" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="29">
-        <v>55</v>
-      </c>
-      <c r="D70" s="23">
-        <v>66</v>
-      </c>
-      <c r="E70" s="24" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A70" s="49"/>
+      <c r="B70" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="28">
+        <v>26</v>
+      </c>
+      <c r="D70" s="21">
+        <v>17</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>6</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="J70" s="29">
-        <v>36</v>
-      </c>
-      <c r="K70" s="23">
-        <v>15</v>
-      </c>
-      <c r="L70" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="51" t="s">
-        <v>31</v>
-      </c>
+      <c r="H70" s="49"/>
+      <c r="I70" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J70" s="28">
+        <v>57</v>
+      </c>
+      <c r="K70" s="21">
+        <v>71</v>
+      </c>
+      <c r="L70" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A71" s="49"/>
       <c r="B71" s="30" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71" s="32">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D71" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>5</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="51" t="s">
-        <v>31</v>
-      </c>
+      <c r="H71" s="49"/>
       <c r="I71" s="30" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J71" s="32">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K71" s="2">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="L71" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A72" s="52"/>
-      <c r="B72" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C72" s="16">
-        <v>32</v>
-      </c>
-      <c r="D72" s="21">
-        <v>22</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="50"/>
+      <c r="B72" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="29">
+        <v>55</v>
+      </c>
+      <c r="D72" s="23">
+        <v>66</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J72" s="16">
-        <v>51</v>
-      </c>
-      <c r="K72" s="21">
-        <v>62</v>
-      </c>
-      <c r="L72" s="22" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="52"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="29">
+        <v>36</v>
+      </c>
+      <c r="K72" s="23">
+        <v>15</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="46" t="s">
+        <v>31</v>
+      </c>
       <c r="B73" s="30" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" s="32">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D73" s="2">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="52"/>
+      <c r="H73" s="46" t="s">
+        <v>31</v>
+      </c>
       <c r="I73" s="30" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J73" s="32">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K73" s="2">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="L73" s="34" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A74" s="52"/>
+      <c r="A74" s="47"/>
       <c r="B74" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C74" s="16">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D74" s="21">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="E74" s="22" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="52"/>
+      <c r="H74" s="47"/>
       <c r="I74" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J74" s="16">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="K74" s="21">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L74" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A75" s="47"/>
+      <c r="B75" s="30" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A75" s="52"/>
-      <c r="B75" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C75" s="20">
-        <v>80</v>
-      </c>
-      <c r="D75" s="25">
-        <v>8</v>
-      </c>
-      <c r="E75" s="26" t="s">
-        <v>5</v>
+      <c r="C75" s="32">
+        <v>84</v>
+      </c>
+      <c r="D75" s="2">
+        <v>31</v>
+      </c>
+      <c r="E75" s="34" t="s">
+        <v>8</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="19" t="s">
+      <c r="H75" s="47"/>
+      <c r="I75" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J75" s="32">
+        <v>82</v>
+      </c>
+      <c r="K75" s="2">
+        <v>3</v>
+      </c>
+      <c r="L75" s="34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A76" s="47"/>
+      <c r="B76" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="16">
+        <v>53</v>
+      </c>
+      <c r="D76" s="21">
+        <v>69</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="16">
+        <v>29</v>
+      </c>
+      <c r="K76" s="21">
+        <v>93</v>
+      </c>
+      <c r="L76" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J75" s="20">
+    </row>
+    <row r="77" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A77" s="47"/>
+      <c r="B77" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="20">
+        <v>80</v>
+      </c>
+      <c r="D77" s="25">
+        <v>8</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="47"/>
+      <c r="I77" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J77" s="20">
         <v>94</v>
       </c>
-      <c r="K75" s="25">
+      <c r="K77" s="25">
         <v>18</v>
       </c>
-      <c r="L75" s="26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-    </row>
-    <row r="78" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A78" s="45" t="s">
+      <c r="L77" s="26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+    </row>
+    <row r="80" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+      <c r="A80" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45"/>
-    </row>
-    <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="46" t="s">
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+    </row>
+    <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A81" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="46"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="46" t="s">
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
+      <c r="D81" s="48"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="I79" s="46"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-    </row>
-    <row r="80" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="8" t="s">
+      <c r="I81" s="48"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
+      <c r="L81" s="48"/>
+    </row>
+    <row r="82" spans="1:12" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C82" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D82" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="8" t="s">
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I80" s="9" t="s">
+      <c r="I82" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J82" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K82" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L80" s="9" t="s">
+      <c r="L82" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A81" s="57" t="s">
+    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A83" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B83" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C83" s="16">
         <v>59</v>
       </c>
-      <c r="D81" s="21">
+      <c r="D83" s="21">
         <v>92</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E83" s="22" t="s">
         <v>4</v>
-      </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="5"/>
-      <c r="H81" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="I81" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="16">
-        <v>3</v>
-      </c>
-      <c r="K81" s="21">
-        <v>15</v>
-      </c>
-      <c r="L81" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A82" s="57"/>
-      <c r="B82" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C82" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="2">
-        <v>69</v>
-      </c>
-      <c r="E82" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="53"/>
-      <c r="I82" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="J82" s="32">
-        <v>35</v>
-      </c>
-      <c r="K82" s="2">
-        <v>94</v>
-      </c>
-      <c r="L82" s="34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A83" s="57"/>
-      <c r="B83" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="28">
-        <v>10</v>
-      </c>
-      <c r="D83" s="21">
-        <v>23</v>
-      </c>
-      <c r="E83" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="53"/>
+      <c r="H83" s="49" t="s">
+        <v>26</v>
+      </c>
       <c r="I83" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J83" s="28">
-        <v>51</v>
+        <v>5</v>
+      </c>
+      <c r="J83" s="16">
+        <v>3</v>
       </c>
       <c r="K83" s="21">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="L83" s="22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A84" s="57"/>
+      <c r="A84" s="53"/>
       <c r="B84" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="32">
-        <v>29</v>
+        <v>2</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>3</v>
       </c>
       <c r="D84" s="2">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="53"/>
+      <c r="H84" s="49"/>
       <c r="I84" s="30" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J84" s="32">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="K84" s="2">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="L84" s="34" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="58"/>
-      <c r="B85" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="27">
-        <v>55</v>
-      </c>
-      <c r="D85" s="35">
-        <v>86</v>
-      </c>
-      <c r="E85" s="36" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A85" s="53"/>
+      <c r="B85" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="28">
+        <v>10</v>
+      </c>
+      <c r="D85" s="21">
+        <v>23</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>6</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="54"/>
-      <c r="I85" s="17" t="s">
+      <c r="H85" s="49"/>
+      <c r="I85" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J85" s="28">
+        <v>51</v>
+      </c>
+      <c r="K85" s="21">
+        <v>93</v>
+      </c>
+      <c r="L85" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A86" s="53"/>
+      <c r="B86" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="32">
+        <v>29</v>
+      </c>
+      <c r="D86" s="2">
+        <v>6</v>
+      </c>
+      <c r="E86" s="34" t="s">
         <v>5</v>
-      </c>
-      <c r="J85" s="29">
-        <v>1</v>
-      </c>
-      <c r="K85" s="23">
-        <v>17</v>
-      </c>
-      <c r="L85" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="B86" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C86" s="33">
-        <v>75</v>
-      </c>
-      <c r="D86" s="37">
-        <v>68</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>1</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="51" t="s">
-        <v>25</v>
-      </c>
+      <c r="H86" s="49"/>
       <c r="I86" s="30" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J86" s="32">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="K86" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L86" s="34" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="56"/>
-      <c r="B87" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="16">
-        <v>11</v>
-      </c>
-      <c r="D87" s="21">
-        <v>22</v>
-      </c>
-      <c r="E87" s="22" t="s">
-        <v>6</v>
+    <row r="87" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="54"/>
+      <c r="B87" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="27">
+        <v>55</v>
+      </c>
+      <c r="D87" s="35">
+        <v>86</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>4</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J87" s="16">
-        <v>57</v>
-      </c>
-      <c r="K87" s="21">
-        <v>83</v>
-      </c>
-      <c r="L87" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="56"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J87" s="29">
+        <v>1</v>
+      </c>
+      <c r="K87" s="23">
+        <v>17</v>
+      </c>
+      <c r="L87" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="B88" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="32">
-        <v>31</v>
-      </c>
-      <c r="D88" s="2">
-        <v>18</v>
-      </c>
-      <c r="E88" s="34" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="C88" s="33">
+        <v>75</v>
+      </c>
+      <c r="D88" s="37">
+        <v>68</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>1</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="52"/>
+      <c r="H88" s="46" t="s">
+        <v>25</v>
+      </c>
       <c r="I88" s="30" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J88" s="32">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="K88" s="2">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="L88" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A89" s="56"/>
+      <c r="A89" s="52"/>
       <c r="B89" s="14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C89" s="16">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D89" s="21">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F89" s="4"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="52"/>
+      <c r="H89" s="47"/>
       <c r="I89" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J89" s="16">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="K89" s="21">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="L89" s="22" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A90" s="56"/>
-      <c r="B90" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C90" s="20">
-        <v>82</v>
-      </c>
-      <c r="D90" s="25">
-        <v>66</v>
-      </c>
-      <c r="E90" s="26" t="s">
-        <v>1</v>
+      <c r="A90" s="52"/>
+      <c r="B90" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="32">
+        <v>31</v>
+      </c>
+      <c r="D90" s="2">
+        <v>18</v>
+      </c>
+      <c r="E90" s="34" t="s">
+        <v>6</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J90" s="20">
+      <c r="H90" s="47"/>
+      <c r="I90" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J90" s="32">
+        <v>77</v>
+      </c>
+      <c r="K90" s="2">
+        <v>71</v>
+      </c>
+      <c r="L90" s="34" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A91" s="52"/>
+      <c r="B91" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="16">
+        <v>53</v>
+      </c>
+      <c r="D91" s="21">
+        <v>84</v>
+      </c>
+      <c r="E91" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="47"/>
+      <c r="I91" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="16">
+        <v>8</v>
+      </c>
+      <c r="K91" s="21">
+        <v>36</v>
+      </c>
+      <c r="L91" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="20" x14ac:dyDescent="0.15">
+      <c r="A92" s="52"/>
+      <c r="B92" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="20">
+        <v>82</v>
+      </c>
+      <c r="D92" s="25">
+        <v>66</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="47"/>
+      <c r="I92" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J92" s="20">
         <v>26</v>
       </c>
-      <c r="K90" s="25">
+      <c r="K92" s="25">
         <v>20</v>
       </c>
-      <c r="L90" s="26" t="s">
+      <c r="L92" s="26" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="H86:H90"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="H64:L64"/>
-    <mergeCell ref="A66:A70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="A71:A75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="H79:L79"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="H81:H85"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="H26:H30"/>
+  <mergeCells count="43">
+    <mergeCell ref="A88:A92"/>
+    <mergeCell ref="H88:H92"/>
+    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="H66:L66"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="H68:H72"/>
+    <mergeCell ref="A73:A77"/>
+    <mergeCell ref="H73:H77"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="H81:L81"/>
+    <mergeCell ref="A83:A87"/>
+    <mergeCell ref="H83:H87"/>
+    <mergeCell ref="A58:A62"/>
+    <mergeCell ref="H58:H62"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="H36:L36"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="H38:H42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="H51:L51"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="H53:H57"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="H4:L4"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="H28:H32"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="H8:H12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="H13:H17"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="H23:H27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B6:C15 B21:C30 B36:C45 B51:C60 B66:C75 B81:C90">
+  <conditionalFormatting sqref="B8:C17 B23:C32 B38:C47 B53:C62 B68:C77 B83:C92">
     <cfRule type="expression" dxfId="55" priority="49">
-      <formula>AND($B6="2a",$B$1=TRUE)</formula>
+      <formula>AND($B8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="54" priority="48">
-      <formula>AND($B6="2b",$C$1=TRUE)</formula>
+      <formula>AND($B8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="53" priority="47">
-      <formula>AND($B6="2c",$D$1=TRUE)</formula>
+      <formula>AND($B8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="52" priority="46">
-      <formula>AND($B6="2d",$E$1=TRUE)</formula>
+      <formula>AND($B8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="51" priority="45">
-      <formula>AND($B6="2e",$I$1=TRUE)</formula>
+      <formula>AND($B8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="50" priority="44">
-      <formula>AND($B6="2f",$J$1=TRUE)</formula>
+      <formula>AND($B8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="49" priority="43">
-      <formula>AND($B6="2g",$K$1=TRUE)</formula>
+      <formula>AND($B8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:E15 D21:E30 D36:E45 D51:E60 D66:E75 D81:E90">
+  <conditionalFormatting sqref="D8:E17 D23:E32 D38:E47 D53:E62 D68:E77 D83:E92">
     <cfRule type="expression" dxfId="48" priority="15">
-      <formula>AND($E6="2g",$K$1=TRUE)</formula>
+      <formula>AND($E8="2g",$K$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="16">
-      <formula>AND($E6="2f",$J$1=TRUE)</formula>
+      <formula>AND($E8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="46" priority="17">
-      <formula>AND($E6="2e",$I$1=TRUE)</formula>
+      <formula>AND($E8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="45" priority="18">
-      <formula>AND($E6="2d",$E$1=TRUE)</formula>
+      <formula>AND($E8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="44" priority="19">
-      <formula>AND($E6="2c",$D$1=TRUE)</formula>
+      <formula>AND($E8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="43" priority="20">
-      <formula>AND($E6="2b",$C$1=TRUE)</formula>
+      <formula>AND($E8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="21">
-      <formula>AND($E6="2a",$B$1=TRUE)</formula>
+      <formula>AND($E8="2a",$B$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:J15 I21:J30 I36:J45 I51:J60 I66:J75 I81:J90">
+  <conditionalFormatting sqref="I8:J17 I23:J32 I38:J47 I53:J62 I68:J77 I83:J92">
     <cfRule type="expression" dxfId="41" priority="9">
-      <formula>AND($I6="2f",$J$1=TRUE)</formula>
+      <formula>AND($I8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="40" priority="10">
-      <formula>AND($I6="2e",$I$1=TRUE)</formula>
+      <formula>AND($I8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="11">
-      <formula>AND($I6="2d",$E$1=TRUE)</formula>
+      <formula>AND($I8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="38" priority="12">
-      <formula>AND($I6="2c",$D$1=TRUE)</formula>
+      <formula>AND($I8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="37" priority="13">
-      <formula>AND($I6="2b",$C$1=TRUE)</formula>
+      <formula>AND($I8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="36" priority="14">
-      <formula>AND($I6="2a",$B$1=TRUE)</formula>
+      <formula>AND($I8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="35" priority="8">
-      <formula>AND($I6="2g",$K$1=TRUE)</formula>
+      <formula>AND($I8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:L15 K21:L30 K36:L45 K51:L60 K66:L75 K81:L90">
+  <conditionalFormatting sqref="K8:L17 K23:L32 K38:L47 K53:L62 K68:L77 K83:L92">
     <cfRule type="expression" dxfId="34" priority="7">
-      <formula>AND($L6="2a",$B$1=TRUE)</formula>
+      <formula>AND($L8="2a",$B$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="33" priority="6">
-      <formula>AND($L6="2b",$C$1=TRUE)</formula>
+      <formula>AND($L8="2b",$C$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="32" priority="5">
-      <formula>AND($L6="2c",$D$1=TRUE)</formula>
+      <formula>AND($L8="2c",$D$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="31" priority="4">
-      <formula>AND($L6="2d",$E$1=TRUE)</formula>
+      <formula>AND($L8="2d",$E$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="30" priority="3">
-      <formula>AND($L6="2e",$I$1=TRUE)</formula>
+      <formula>AND($L8="2e",$I$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="29" priority="2">
-      <formula>AND($L6="2f",$J$1=TRUE)</formula>
+      <formula>AND($L8="2f",$J$1=TRUE)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="28" priority="1">
-      <formula>AND($L6="2g",$K$1=TRUE)</formula>
+      <formula>AND($L8="2g",$K$1=TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="44" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -4870,19 +4894,19 @@
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A2" s="41"/>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="42"/>
@@ -4913,7 +4937,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="55" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="14" t="s">
@@ -4943,7 +4967,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A5" s="47"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="14" t="s">
         <v>5</v>
       </c>
@@ -4971,7 +4995,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="47"/>
+      <c r="A6" s="55"/>
       <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
@@ -4999,7 +5023,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
+      <c r="A7" s="55"/>
       <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
@@ -5027,7 +5051,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48"/>
+      <c r="A8" s="56"/>
       <c r="B8" s="17" t="s">
         <v>5</v>
       </c>
@@ -5055,7 +5079,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="58" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -5085,7 +5109,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
+      <c r="A10" s="57"/>
       <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
@@ -5113,7 +5137,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="49"/>
+      <c r="A11" s="57"/>
       <c r="B11" s="14" t="s">
         <v>5</v>
       </c>
@@ -5141,7 +5165,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="14" t="s">
         <v>6</v>
       </c>
@@ -5169,7 +5193,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A13" s="49"/>
+      <c r="A13" s="57"/>
       <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
@@ -5224,19 +5248,19 @@
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="41"/>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
     </row>
     <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="42"/>
@@ -5267,10 +5291,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="27">
@@ -5297,8 +5321,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="47"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="55"/>
+      <c r="B19" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="16">
@@ -5325,8 +5349,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="47"/>
-      <c r="B20" s="21" t="s">
+      <c r="A20" s="55"/>
+      <c r="B20" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="28">
@@ -5353,8 +5377,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="55"/>
+      <c r="B21" s="14" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="16">
@@ -5381,8 +5405,8 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
-      <c r="B22" s="23" t="s">
+      <c r="A22" s="56"/>
+      <c r="B22" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="29">
@@ -5409,10 +5433,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="20">
@@ -5439,8 +5463,8 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="57"/>
+      <c r="B24" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="16">
@@ -5467,8 +5491,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A25" s="49"/>
-      <c r="B25" s="21" t="s">
+      <c r="A25" s="57"/>
+      <c r="B25" s="14" t="s">
         <v>4</v>
       </c>
       <c r="C25" s="16">
@@ -5495,8 +5519,8 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="49"/>
-      <c r="B26" s="21" t="s">
+      <c r="A26" s="57"/>
+      <c r="B26" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="16">
@@ -5523,8 +5547,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="57"/>
+      <c r="B27" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="16">
@@ -5578,19 +5602,19 @@
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
-      <c r="B30" s="46" t="s">
+      <c r="B30" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="46" t="s">
+      <c r="G30" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
     </row>
     <row r="31" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="42"/>
@@ -5621,7 +5645,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="55" t="s">
         <v>27</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -5651,7 +5675,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A33" s="47"/>
+      <c r="A33" s="55"/>
       <c r="B33" s="14" t="s">
         <v>2</v>
       </c>
@@ -5679,7 +5703,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="47"/>
+      <c r="A34" s="55"/>
       <c r="B34" s="30" t="s">
         <v>5</v>
       </c>
@@ -5707,7 +5731,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="47"/>
+      <c r="A35" s="55"/>
       <c r="B35" s="14" t="s">
         <v>1</v>
       </c>
@@ -5735,7 +5759,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
+      <c r="A36" s="55"/>
       <c r="B36" s="17" t="s">
         <v>7</v>
       </c>
@@ -5763,7 +5787,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="58" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="19" t="s">
@@ -5793,7 +5817,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="49"/>
+      <c r="A38" s="57"/>
       <c r="B38" s="30" t="s">
         <v>5</v>
       </c>
@@ -5821,7 +5845,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
@@ -5849,7 +5873,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="49"/>
+      <c r="A40" s="57"/>
       <c r="B40" s="30" t="s">
         <v>7</v>
       </c>
@@ -5877,7 +5901,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A41" s="49"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="14" t="s">
         <v>2</v>
       </c>
@@ -5932,19 +5956,19 @@
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="46"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="46" t="s">
+      <c r="G44" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
     </row>
     <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="42"/>
@@ -5975,7 +5999,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="55" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -6005,7 +6029,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="47"/>
+      <c r="A47" s="55"/>
       <c r="B47" s="30" t="s">
         <v>2</v>
       </c>
@@ -6033,7 +6057,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="47"/>
+      <c r="A48" s="55"/>
       <c r="B48" s="14" t="s">
         <v>5</v>
       </c>
@@ -6061,7 +6085,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A49" s="47"/>
+      <c r="A49" s="55"/>
       <c r="B49" s="30" t="s">
         <v>8</v>
       </c>
@@ -6089,7 +6113,7 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="48"/>
+      <c r="A50" s="56"/>
       <c r="B50" s="17" t="s">
         <v>7</v>
       </c>
@@ -6117,7 +6141,7 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="57" t="s">
         <v>30</v>
       </c>
       <c r="B51" s="30" t="s">
@@ -6147,7 +6171,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A52" s="49"/>
+      <c r="A52" s="57"/>
       <c r="B52" s="14" t="s">
         <v>5</v>
       </c>
@@ -6175,7 +6199,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A53" s="49"/>
+      <c r="A53" s="57"/>
       <c r="B53" s="30" t="s">
         <v>8</v>
       </c>
@@ -6203,7 +6227,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A54" s="49"/>
+      <c r="A54" s="57"/>
       <c r="B54" s="14" t="s">
         <v>7</v>
       </c>
@@ -6231,7 +6255,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A55" s="49"/>
+      <c r="A55" s="57"/>
       <c r="B55" s="19" t="s">
         <v>2</v>
       </c>
@@ -6286,19 +6310,19 @@
     </row>
     <row r="58" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
-      <c r="B58" s="46" t="s">
+      <c r="B58" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
+      <c r="C58" s="48"/>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="46" t="s">
+      <c r="G58" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="46"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
     </row>
     <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="42"/>
@@ -6329,7 +6353,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="55" t="s">
         <v>24</v>
       </c>
       <c r="B60" s="14" t="s">
@@ -6359,7 +6383,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A61" s="47"/>
+      <c r="A61" s="55"/>
       <c r="B61" s="30" t="s">
         <v>2</v>
       </c>
@@ -6387,7 +6411,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A62" s="47"/>
+      <c r="A62" s="55"/>
       <c r="B62" s="14" t="s">
         <v>8</v>
       </c>
@@ -6415,7 +6439,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A63" s="47"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="30" t="s">
         <v>4</v>
       </c>
@@ -6443,7 +6467,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
+      <c r="A64" s="55"/>
       <c r="B64" s="17" t="s">
         <v>7</v>
       </c>
@@ -6471,7 +6495,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="50" t="s">
+      <c r="A65" s="58" t="s">
         <v>31</v>
       </c>
       <c r="B65" s="30" t="s">
@@ -6501,7 +6525,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A66" s="49"/>
+      <c r="A66" s="57"/>
       <c r="B66" s="14" t="s">
         <v>8</v>
       </c>
@@ -6529,7 +6553,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A67" s="49"/>
+      <c r="A67" s="57"/>
       <c r="B67" s="30" t="s">
         <v>4</v>
       </c>
@@ -6557,7 +6581,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A68" s="49"/>
+      <c r="A68" s="57"/>
       <c r="B68" s="14" t="s">
         <v>7</v>
       </c>
@@ -6585,7 +6609,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A69" s="49"/>
+      <c r="A69" s="57"/>
       <c r="B69" s="19" t="s">
         <v>2</v>
       </c>
@@ -6640,19 +6664,19 @@
     </row>
     <row r="72" spans="1:10" ht="20" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
-      <c r="B72" s="46" t="s">
+      <c r="B72" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="46" t="s">
+      <c r="G72" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
     </row>
     <row r="73" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="42"/>
@@ -6683,7 +6707,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A74" s="47" t="s">
+      <c r="A74" s="55" t="s">
         <v>26</v>
       </c>
       <c r="B74" s="14" t="s">
@@ -6713,7 +6737,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
+      <c r="A75" s="55"/>
       <c r="B75" s="30" t="s">
         <v>2</v>
       </c>
@@ -6741,7 +6765,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
+      <c r="A76" s="55"/>
       <c r="B76" s="14" t="s">
         <v>5</v>
       </c>
@@ -6769,7 +6793,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A77" s="47"/>
+      <c r="A77" s="55"/>
       <c r="B77" s="30" t="s">
         <v>8</v>
       </c>
@@ -6797,7 +6821,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+      <c r="A78" s="56"/>
       <c r="B78" s="17" t="s">
         <v>7</v>
       </c>
@@ -6825,7 +6849,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="21" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="49" t="s">
+      <c r="A79" s="57" t="s">
         <v>25</v>
       </c>
       <c r="B79" s="30" t="s">
@@ -6855,7 +6879,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
+      <c r="A80" s="57"/>
       <c r="B80" s="14" t="s">
         <v>5</v>
       </c>
@@ -6883,7 +6907,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A81" s="49"/>
+      <c r="A81" s="57"/>
       <c r="B81" s="30" t="s">
         <v>8</v>
       </c>
@@ -6911,7 +6935,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A82" s="49"/>
+      <c r="A82" s="57"/>
       <c r="B82" s="14" t="s">
         <v>7</v>
       </c>
@@ -6939,7 +6963,7 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A83" s="49"/>
+      <c r="A83" s="57"/>
       <c r="B83" s="19" t="s">
         <v>2</v>
       </c>
@@ -7092,19 +7116,11 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -7351,12 +7367,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
@@ -7374,15 +7390,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7401,7 +7418,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
@@ -7409,7 +7426,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -7424,4 +7441,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>